--- a/thaco/API/1 MID- VPTQ THACO-11FEBv2.xlsx
+++ b/thaco/API/1 MID- VPTQ THACO-11FEBv2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/API/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41759FF6-5E30-744C-94D5-3F1E3CD12A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C28240B-056C-BE41-AADB-0E19068EF2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="660" windowWidth="38400" windowHeight="21100" tabRatio="761" activeTab="2" xr2:uid="{D2D6ECD8-DC99-4D28-8DAC-0623419D46D2}"/>
+    <workbookView xWindow="38400" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="761" activeTab="2" xr2:uid="{D2D6ECD8-DC99-4D28-8DAC-0623419D46D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="1" r:id="rId1"/>
@@ -4431,7 +4431,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="158">
   <si>
     <t>CÔNG TY …..............</t>
   </si>
@@ -6262,6 +6262,183 @@
     <xf numFmtId="165" fontId="7" fillId="3" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="39" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="6" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="3" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="3" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="3" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6271,21 +6448,6 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="7" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6322,172 +6484,37 @@
     <xf numFmtId="9" fontId="4" fillId="3" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="27" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="27" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="6" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="6" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="3" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="3" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="3" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="45" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="45" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="45" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="39" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="44" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="44" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="44" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6499,6 +6526,60 @@
     <xf numFmtId="165" fontId="10" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="2" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="2" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="10" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6508,175 +6589,172 @@
     <xf numFmtId="165" fontId="10" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="10" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="5" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="5" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="5" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="2" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="2" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="5" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="48" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6688,75 +6766,6 @@
     <xf numFmtId="165" fontId="48" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="5" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="5" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="5" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="5" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="11" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6765,15 +6774,6 @@
     </xf>
     <xf numFmtId="165" fontId="11" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -7566,91 +7566,91 @@
       <c r="CD2" s="193"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="315" t="str">
+      <c r="A3" s="270" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
         <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
       </c>
-      <c r="B3" s="315"/>
-      <c r="C3" s="315"/>
-      <c r="D3" s="315"/>
-      <c r="E3" s="315"/>
-      <c r="F3" s="315"/>
-      <c r="G3" s="315"/>
-      <c r="H3" s="315"/>
-      <c r="I3" s="315"/>
-      <c r="J3" s="315"/>
-      <c r="K3" s="315"/>
-      <c r="L3" s="315"/>
-      <c r="M3" s="315"/>
-      <c r="N3" s="315"/>
-      <c r="O3" s="315"/>
-      <c r="P3" s="315"/>
-      <c r="Q3" s="315"/>
-      <c r="R3" s="315"/>
-      <c r="S3" s="315"/>
-      <c r="T3" s="315"/>
-      <c r="U3" s="315"/>
-      <c r="V3" s="315"/>
-      <c r="W3" s="315"/>
-      <c r="X3" s="315"/>
-      <c r="Y3" s="315"/>
-      <c r="Z3" s="315"/>
-      <c r="AA3" s="315"/>
-      <c r="AB3" s="315"/>
-      <c r="AC3" s="315"/>
-      <c r="AD3" s="315"/>
-      <c r="AE3" s="315"/>
-      <c r="AF3" s="315"/>
-      <c r="AG3" s="315"/>
-      <c r="AH3" s="315"/>
-      <c r="AI3" s="315"/>
-      <c r="AJ3" s="315"/>
-      <c r="AK3" s="315"/>
-      <c r="AL3" s="315"/>
-      <c r="AM3" s="315"/>
-      <c r="AN3" s="315"/>
-      <c r="AO3" s="315"/>
-      <c r="AP3" s="315"/>
-      <c r="AQ3" s="315"/>
-      <c r="AR3" s="315"/>
-      <c r="AS3" s="315"/>
-      <c r="AT3" s="315"/>
-      <c r="AU3" s="315"/>
-      <c r="AV3" s="315"/>
-      <c r="AW3" s="315"/>
-      <c r="AX3" s="315"/>
-      <c r="AY3" s="315"/>
-      <c r="AZ3" s="315"/>
-      <c r="BA3" s="315"/>
-      <c r="BB3" s="315"/>
-      <c r="BC3" s="315"/>
-      <c r="BD3" s="315"/>
-      <c r="BE3" s="315"/>
-      <c r="BF3" s="315"/>
-      <c r="BG3" s="315"/>
-      <c r="BH3" s="315"/>
-      <c r="BI3" s="315"/>
-      <c r="BJ3" s="315"/>
-      <c r="BK3" s="315"/>
-      <c r="BL3" s="315"/>
-      <c r="BM3" s="315"/>
-      <c r="BN3" s="315"/>
-      <c r="BO3" s="315"/>
-      <c r="BP3" s="315"/>
-      <c r="BQ3" s="315"/>
-      <c r="BR3" s="315"/>
-      <c r="BS3" s="315"/>
-      <c r="BT3" s="315"/>
-      <c r="BU3" s="315"/>
+      <c r="B3" s="270"/>
+      <c r="C3" s="270"/>
+      <c r="D3" s="270"/>
+      <c r="E3" s="270"/>
+      <c r="F3" s="270"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="270"/>
+      <c r="I3" s="270"/>
+      <c r="J3" s="270"/>
+      <c r="K3" s="270"/>
+      <c r="L3" s="270"/>
+      <c r="M3" s="270"/>
+      <c r="N3" s="270"/>
+      <c r="O3" s="270"/>
+      <c r="P3" s="270"/>
+      <c r="Q3" s="270"/>
+      <c r="R3" s="270"/>
+      <c r="S3" s="270"/>
+      <c r="T3" s="270"/>
+      <c r="U3" s="270"/>
+      <c r="V3" s="270"/>
+      <c r="W3" s="270"/>
+      <c r="X3" s="270"/>
+      <c r="Y3" s="270"/>
+      <c r="Z3" s="270"/>
+      <c r="AA3" s="270"/>
+      <c r="AB3" s="270"/>
+      <c r="AC3" s="270"/>
+      <c r="AD3" s="270"/>
+      <c r="AE3" s="270"/>
+      <c r="AF3" s="270"/>
+      <c r="AG3" s="270"/>
+      <c r="AH3" s="270"/>
+      <c r="AI3" s="270"/>
+      <c r="AJ3" s="270"/>
+      <c r="AK3" s="270"/>
+      <c r="AL3" s="270"/>
+      <c r="AM3" s="270"/>
+      <c r="AN3" s="270"/>
+      <c r="AO3" s="270"/>
+      <c r="AP3" s="270"/>
+      <c r="AQ3" s="270"/>
+      <c r="AR3" s="270"/>
+      <c r="AS3" s="270"/>
+      <c r="AT3" s="270"/>
+      <c r="AU3" s="270"/>
+      <c r="AV3" s="270"/>
+      <c r="AW3" s="270"/>
+      <c r="AX3" s="270"/>
+      <c r="AY3" s="270"/>
+      <c r="AZ3" s="270"/>
+      <c r="BA3" s="270"/>
+      <c r="BB3" s="270"/>
+      <c r="BC3" s="270"/>
+      <c r="BD3" s="270"/>
+      <c r="BE3" s="270"/>
+      <c r="BF3" s="270"/>
+      <c r="BG3" s="270"/>
+      <c r="BH3" s="270"/>
+      <c r="BI3" s="270"/>
+      <c r="BJ3" s="270"/>
+      <c r="BK3" s="270"/>
+      <c r="BL3" s="270"/>
+      <c r="BM3" s="270"/>
+      <c r="BN3" s="270"/>
+      <c r="BO3" s="270"/>
+      <c r="BP3" s="270"/>
+      <c r="BQ3" s="270"/>
+      <c r="BR3" s="270"/>
+      <c r="BS3" s="270"/>
+      <c r="BT3" s="270"/>
+      <c r="BU3" s="270"/>
       <c r="BV3" s="195"/>
-      <c r="BW3" s="293" t="s">
+      <c r="BW3" s="274" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="293"/>
-      <c r="BY3" s="293"/>
-      <c r="BZ3" s="293"/>
-      <c r="CA3" s="293"/>
-      <c r="CB3" s="294"/>
+      <c r="BX3" s="274"/>
+      <c r="BY3" s="274"/>
+      <c r="BZ3" s="274"/>
+      <c r="CA3" s="274"/>
+      <c r="CB3" s="275"/>
       <c r="CC3" s="196"/>
       <c r="CD3" s="196"/>
     </row>
@@ -7728,12 +7728,12 @@
       <c r="BT4" s="197"/>
       <c r="BU4" s="197"/>
       <c r="BV4" s="197"/>
-      <c r="BW4" s="294"/>
-      <c r="BX4" s="294"/>
-      <c r="BY4" s="294"/>
-      <c r="BZ4" s="294"/>
-      <c r="CA4" s="294"/>
-      <c r="CB4" s="294"/>
+      <c r="BW4" s="275"/>
+      <c r="BX4" s="275"/>
+      <c r="BY4" s="275"/>
+      <c r="BZ4" s="275"/>
+      <c r="CA4" s="275"/>
+      <c r="CB4" s="275"/>
       <c r="CC4" s="196"/>
       <c r="CD4" s="196"/>
     </row>
@@ -7811,12 +7811,12 @@
       <c r="BT5" s="197"/>
       <c r="BU5" s="197"/>
       <c r="BV5" s="197"/>
-      <c r="BW5" s="294"/>
-      <c r="BX5" s="294"/>
-      <c r="BY5" s="294"/>
-      <c r="BZ5" s="294"/>
-      <c r="CA5" s="294"/>
-      <c r="CB5" s="294"/>
+      <c r="BW5" s="275"/>
+      <c r="BX5" s="275"/>
+      <c r="BY5" s="275"/>
+      <c r="BZ5" s="275"/>
+      <c r="CA5" s="275"/>
+      <c r="CB5" s="275"/>
       <c r="CC5" s="196"/>
       <c r="CD5" s="196"/>
     </row>
@@ -7894,12 +7894,12 @@
       <c r="BT6" s="199"/>
       <c r="BU6" s="199"/>
       <c r="BV6" s="199"/>
-      <c r="BW6" s="293"/>
-      <c r="BX6" s="293"/>
-      <c r="BY6" s="293"/>
-      <c r="BZ6" s="293"/>
-      <c r="CA6" s="293"/>
-      <c r="CB6" s="294"/>
+      <c r="BW6" s="274"/>
+      <c r="BX6" s="274"/>
+      <c r="BY6" s="274"/>
+      <c r="BZ6" s="274"/>
+      <c r="CA6" s="274"/>
+      <c r="CB6" s="275"/>
       <c r="CC6" s="196"/>
       <c r="CD6" s="196"/>
     </row>
@@ -8052,356 +8052,356 @@
       </c>
     </row>
     <row r="8" spans="1:87" s="150" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="295" t="s">
+      <c r="A8" s="276" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="298" t="s">
+      <c r="B8" s="279" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="247" t="s">
+      <c r="C8" s="261" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="301" t="s">
+      <c r="D8" s="271" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="301" t="s">
+      <c r="E8" s="271" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="247" t="s">
+      <c r="F8" s="261" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="304" t="s">
+      <c r="G8" s="258" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="272" t="s">
+      <c r="H8" s="288" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="272" t="s">
+      <c r="I8" s="288" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="304" t="s">
+      <c r="J8" s="258" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="275" t="s">
+      <c r="K8" s="291" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="276"/>
-      <c r="M8" s="276"/>
-      <c r="N8" s="276"/>
-      <c r="O8" s="276"/>
-      <c r="P8" s="276"/>
-      <c r="Q8" s="276"/>
-      <c r="R8" s="276"/>
-      <c r="S8" s="276"/>
-      <c r="T8" s="276"/>
-      <c r="U8" s="276"/>
-      <c r="V8" s="276"/>
-      <c r="W8" s="276"/>
-      <c r="X8" s="276"/>
-      <c r="Y8" s="277" t="s">
+      <c r="L8" s="292"/>
+      <c r="M8" s="292"/>
+      <c r="N8" s="292"/>
+      <c r="O8" s="292"/>
+      <c r="P8" s="292"/>
+      <c r="Q8" s="292"/>
+      <c r="R8" s="292"/>
+      <c r="S8" s="292"/>
+      <c r="T8" s="292"/>
+      <c r="U8" s="292"/>
+      <c r="V8" s="292"/>
+      <c r="W8" s="292"/>
+      <c r="X8" s="292"/>
+      <c r="Y8" s="293" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="278"/>
-      <c r="AA8" s="278"/>
-      <c r="AB8" s="278"/>
-      <c r="AC8" s="278"/>
-      <c r="AD8" s="278"/>
-      <c r="AE8" s="278"/>
-      <c r="AF8" s="278"/>
-      <c r="AG8" s="278"/>
-      <c r="AH8" s="278"/>
-      <c r="AI8" s="278"/>
-      <c r="AJ8" s="278"/>
-      <c r="AK8" s="278"/>
-      <c r="AL8" s="278"/>
-      <c r="AM8" s="278"/>
-      <c r="AN8" s="278"/>
-      <c r="AO8" s="279"/>
-      <c r="AP8" s="304" t="s">
+      <c r="Z8" s="294"/>
+      <c r="AA8" s="294"/>
+      <c r="AB8" s="294"/>
+      <c r="AC8" s="294"/>
+      <c r="AD8" s="294"/>
+      <c r="AE8" s="294"/>
+      <c r="AF8" s="294"/>
+      <c r="AG8" s="294"/>
+      <c r="AH8" s="294"/>
+      <c r="AI8" s="294"/>
+      <c r="AJ8" s="294"/>
+      <c r="AK8" s="294"/>
+      <c r="AL8" s="294"/>
+      <c r="AM8" s="294"/>
+      <c r="AN8" s="294"/>
+      <c r="AO8" s="295"/>
+      <c r="AP8" s="258" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="304" t="s">
+      <c r="AQ8" s="258" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="304" t="s">
+      <c r="AR8" s="258" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="304" t="s">
+      <c r="AS8" s="258" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="304" t="s">
+      <c r="AT8" s="258" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="304" t="s">
+      <c r="AU8" s="258" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="247" t="s">
+      <c r="AV8" s="261" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="313" t="s">
+      <c r="AW8" s="267" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="247" t="s">
+      <c r="AX8" s="261" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="317" t="s">
+      <c r="AY8" s="264" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="318"/>
-      <c r="BA8" s="318"/>
-      <c r="BB8" s="318"/>
-      <c r="BC8" s="318"/>
-      <c r="BD8" s="318"/>
-      <c r="BE8" s="318"/>
-      <c r="BF8" s="318"/>
-      <c r="BG8" s="318"/>
-      <c r="BH8" s="318"/>
-      <c r="BI8" s="318"/>
-      <c r="BJ8" s="318"/>
-      <c r="BK8" s="318"/>
-      <c r="BL8" s="318"/>
-      <c r="BM8" s="318"/>
-      <c r="BN8" s="318"/>
-      <c r="BO8" s="318"/>
-      <c r="BP8" s="318"/>
-      <c r="BQ8" s="319"/>
-      <c r="BR8" s="264" t="s">
+      <c r="AZ8" s="265"/>
+      <c r="BA8" s="265"/>
+      <c r="BB8" s="265"/>
+      <c r="BC8" s="265"/>
+      <c r="BD8" s="265"/>
+      <c r="BE8" s="265"/>
+      <c r="BF8" s="265"/>
+      <c r="BG8" s="265"/>
+      <c r="BH8" s="265"/>
+      <c r="BI8" s="265"/>
+      <c r="BJ8" s="265"/>
+      <c r="BK8" s="265"/>
+      <c r="BL8" s="265"/>
+      <c r="BM8" s="265"/>
+      <c r="BN8" s="265"/>
+      <c r="BO8" s="265"/>
+      <c r="BP8" s="265"/>
+      <c r="BQ8" s="266"/>
+      <c r="BR8" s="252" t="s">
         <v>26</v>
       </c>
-      <c r="BS8" s="271"/>
-      <c r="BT8" s="247" t="s">
+      <c r="BS8" s="320"/>
+      <c r="BT8" s="261" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="264" t="s">
+      <c r="BU8" s="252" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="220"/>
-      <c r="BW8" s="252" t="s">
+      <c r="BW8" s="306" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="255" t="s">
+      <c r="BX8" s="309" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="256"/>
-      <c r="BZ8" s="256"/>
-      <c r="CA8" s="257"/>
-      <c r="CB8" s="244" t="s">
+      <c r="BY8" s="310"/>
+      <c r="BZ8" s="310"/>
+      <c r="CA8" s="311"/>
+      <c r="CB8" s="303" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="244" t="s">
+      <c r="CC8" s="303" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="244" t="s">
+      <c r="CD8" s="303" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="135"/>
       <c r="CI8" s="135"/>
     </row>
     <row r="9" spans="1:87" s="150" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="296"/>
-      <c r="B9" s="299"/>
-      <c r="C9" s="248"/>
-      <c r="D9" s="302"/>
-      <c r="E9" s="302"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="305"/>
-      <c r="H9" s="273"/>
-      <c r="I9" s="273"/>
-      <c r="J9" s="305"/>
-      <c r="K9" s="280" t="s">
+      <c r="A9" s="277"/>
+      <c r="B9" s="280"/>
+      <c r="C9" s="262"/>
+      <c r="D9" s="272"/>
+      <c r="E9" s="272"/>
+      <c r="F9" s="262"/>
+      <c r="G9" s="259"/>
+      <c r="H9" s="289"/>
+      <c r="I9" s="289"/>
+      <c r="J9" s="259"/>
+      <c r="K9" s="245" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="280" t="s">
+      <c r="L9" s="245" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="280" t="s">
+      <c r="M9" s="245" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="280" t="s">
+      <c r="N9" s="245" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="280" t="s">
+      <c r="O9" s="245" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="280" t="s">
+      <c r="P9" s="245" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="280" t="s">
+      <c r="Q9" s="245" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="280" t="s">
+      <c r="R9" s="245" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="280" t="s">
+      <c r="S9" s="245" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="280" t="s">
+      <c r="T9" s="245" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="280" t="s">
+      <c r="U9" s="245" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="286" t="s">
+      <c r="V9" s="296" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="287"/>
-      <c r="X9" s="280" t="s">
+      <c r="W9" s="297"/>
+      <c r="X9" s="245" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="283" t="s">
+      <c r="Y9" s="255" t="s">
         <v>47</v>
       </c>
-      <c r="Z9" s="283" t="s">
+      <c r="Z9" s="255" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="283" t="s">
+      <c r="AA9" s="255" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="283" t="s">
+      <c r="AB9" s="255" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="283" t="s">
+      <c r="AC9" s="255" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="283" t="s">
+      <c r="AD9" s="255" t="s">
         <v>52</v>
       </c>
-      <c r="AE9" s="283" t="s">
+      <c r="AE9" s="255" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="283" t="s">
+      <c r="AF9" s="255" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="283" t="s">
+      <c r="AG9" s="255" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="283" t="s">
+      <c r="AH9" s="255" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="283" t="s">
+      <c r="AI9" s="255" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="290" t="s">
+      <c r="AJ9" s="300" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="264" t="s">
+      <c r="AK9" s="252" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="313" t="s">
+      <c r="AL9" s="267" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="283" t="s">
+      <c r="AM9" s="255" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="247" t="s">
+      <c r="AN9" s="261" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="247" t="s">
+      <c r="AO9" s="261" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="305"/>
-      <c r="AQ9" s="305"/>
-      <c r="AR9" s="305"/>
-      <c r="AS9" s="305"/>
-      <c r="AT9" s="305"/>
-      <c r="AU9" s="305"/>
-      <c r="AV9" s="248"/>
-      <c r="AW9" s="316"/>
-      <c r="AX9" s="248"/>
-      <c r="AY9" s="307" t="s">
+      <c r="AP9" s="259"/>
+      <c r="AQ9" s="259"/>
+      <c r="AR9" s="259"/>
+      <c r="AS9" s="259"/>
+      <c r="AT9" s="259"/>
+      <c r="AU9" s="259"/>
+      <c r="AV9" s="262"/>
+      <c r="AW9" s="268"/>
+      <c r="AX9" s="262"/>
+      <c r="AY9" s="282" t="s">
         <v>64</v>
       </c>
-      <c r="AZ9" s="308"/>
-      <c r="BA9" s="308"/>
-      <c r="BB9" s="308"/>
-      <c r="BC9" s="308"/>
-      <c r="BD9" s="308"/>
-      <c r="BE9" s="308"/>
-      <c r="BF9" s="308"/>
-      <c r="BG9" s="308"/>
-      <c r="BH9" s="308"/>
-      <c r="BI9" s="308"/>
-      <c r="BJ9" s="308"/>
-      <c r="BK9" s="308"/>
-      <c r="BL9" s="309"/>
-      <c r="BM9" s="310" t="s">
+      <c r="AZ9" s="283"/>
+      <c r="BA9" s="283"/>
+      <c r="BB9" s="283"/>
+      <c r="BC9" s="283"/>
+      <c r="BD9" s="283"/>
+      <c r="BE9" s="283"/>
+      <c r="BF9" s="283"/>
+      <c r="BG9" s="283"/>
+      <c r="BH9" s="283"/>
+      <c r="BI9" s="283"/>
+      <c r="BJ9" s="283"/>
+      <c r="BK9" s="283"/>
+      <c r="BL9" s="284"/>
+      <c r="BM9" s="285" t="s">
         <v>65</v>
       </c>
-      <c r="BN9" s="311"/>
-      <c r="BO9" s="311"/>
-      <c r="BP9" s="311"/>
-      <c r="BQ9" s="312"/>
-      <c r="BR9" s="248" t="s">
+      <c r="BN9" s="286"/>
+      <c r="BO9" s="286"/>
+      <c r="BP9" s="286"/>
+      <c r="BQ9" s="287"/>
+      <c r="BR9" s="262" t="s">
         <v>66</v>
       </c>
-      <c r="BS9" s="248" t="s">
+      <c r="BS9" s="262" t="s">
         <v>67</v>
       </c>
-      <c r="BT9" s="248"/>
-      <c r="BU9" s="265"/>
+      <c r="BT9" s="262"/>
+      <c r="BU9" s="253"/>
       <c r="BV9" s="220"/>
-      <c r="BW9" s="253"/>
-      <c r="BX9" s="258"/>
-      <c r="BY9" s="259"/>
-      <c r="BZ9" s="259"/>
-      <c r="CA9" s="260"/>
-      <c r="CB9" s="245"/>
-      <c r="CC9" s="245"/>
-      <c r="CD9" s="245"/>
+      <c r="BW9" s="307"/>
+      <c r="BX9" s="312"/>
+      <c r="BY9" s="313"/>
+      <c r="BZ9" s="313"/>
+      <c r="CA9" s="314"/>
+      <c r="CB9" s="304"/>
+      <c r="CC9" s="304"/>
+      <c r="CD9" s="304"/>
       <c r="CH9" s="135"/>
       <c r="CI9" s="135"/>
     </row>
     <row r="10" spans="1:87" s="136" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="296"/>
-      <c r="B10" s="299"/>
-      <c r="C10" s="248"/>
-      <c r="D10" s="302"/>
-      <c r="E10" s="302"/>
-      <c r="F10" s="248"/>
-      <c r="G10" s="305"/>
-      <c r="H10" s="273"/>
-      <c r="I10" s="273"/>
-      <c r="J10" s="305"/>
-      <c r="K10" s="281"/>
-      <c r="L10" s="281"/>
-      <c r="M10" s="281"/>
-      <c r="N10" s="281"/>
-      <c r="O10" s="281"/>
-      <c r="P10" s="281"/>
-      <c r="Q10" s="281"/>
-      <c r="R10" s="281"/>
-      <c r="S10" s="281"/>
-      <c r="T10" s="281"/>
-      <c r="U10" s="281"/>
-      <c r="V10" s="288"/>
-      <c r="W10" s="289"/>
-      <c r="X10" s="281"/>
-      <c r="Y10" s="284"/>
-      <c r="Z10" s="284"/>
-      <c r="AA10" s="284"/>
-      <c r="AB10" s="284"/>
-      <c r="AC10" s="284"/>
-      <c r="AD10" s="284"/>
-      <c r="AE10" s="284"/>
-      <c r="AF10" s="284"/>
-      <c r="AG10" s="284"/>
-      <c r="AH10" s="284"/>
-      <c r="AI10" s="284"/>
-      <c r="AJ10" s="291"/>
-      <c r="AK10" s="265"/>
-      <c r="AL10" s="316"/>
-      <c r="AM10" s="284"/>
-      <c r="AN10" s="248"/>
-      <c r="AO10" s="248"/>
-      <c r="AP10" s="305"/>
-      <c r="AQ10" s="305"/>
-      <c r="AR10" s="305"/>
-      <c r="AS10" s="305"/>
-      <c r="AT10" s="305"/>
-      <c r="AU10" s="305"/>
-      <c r="AV10" s="248"/>
-      <c r="AW10" s="316"/>
-      <c r="AX10" s="248"/>
+      <c r="A10" s="277"/>
+      <c r="B10" s="280"/>
+      <c r="C10" s="262"/>
+      <c r="D10" s="272"/>
+      <c r="E10" s="272"/>
+      <c r="F10" s="262"/>
+      <c r="G10" s="259"/>
+      <c r="H10" s="289"/>
+      <c r="I10" s="289"/>
+      <c r="J10" s="259"/>
+      <c r="K10" s="246"/>
+      <c r="L10" s="246"/>
+      <c r="M10" s="246"/>
+      <c r="N10" s="246"/>
+      <c r="O10" s="246"/>
+      <c r="P10" s="246"/>
+      <c r="Q10" s="246"/>
+      <c r="R10" s="246"/>
+      <c r="S10" s="246"/>
+      <c r="T10" s="246"/>
+      <c r="U10" s="246"/>
+      <c r="V10" s="298"/>
+      <c r="W10" s="299"/>
+      <c r="X10" s="246"/>
+      <c r="Y10" s="256"/>
+      <c r="Z10" s="256"/>
+      <c r="AA10" s="256"/>
+      <c r="AB10" s="256"/>
+      <c r="AC10" s="256"/>
+      <c r="AD10" s="256"/>
+      <c r="AE10" s="256"/>
+      <c r="AF10" s="256"/>
+      <c r="AG10" s="256"/>
+      <c r="AH10" s="256"/>
+      <c r="AI10" s="256"/>
+      <c r="AJ10" s="301"/>
+      <c r="AK10" s="253"/>
+      <c r="AL10" s="268"/>
+      <c r="AM10" s="256"/>
+      <c r="AN10" s="262"/>
+      <c r="AO10" s="262"/>
+      <c r="AP10" s="259"/>
+      <c r="AQ10" s="259"/>
+      <c r="AR10" s="259"/>
+      <c r="AS10" s="259"/>
+      <c r="AT10" s="259"/>
+      <c r="AU10" s="259"/>
+      <c r="AV10" s="262"/>
+      <c r="AW10" s="268"/>
+      <c r="AX10" s="262"/>
       <c r="AY10" s="221" t="s">
         <v>68</v>
       </c>
@@ -8411,13 +8411,13 @@
       <c r="BA10" s="221" t="s">
         <v>70</v>
       </c>
-      <c r="BB10" s="267" t="s">
+      <c r="BB10" s="318" t="s">
         <v>71</v>
       </c>
-      <c r="BC10" s="269" t="s">
+      <c r="BC10" s="248" t="s">
         <v>72</v>
       </c>
-      <c r="BD10" s="269" t="s">
+      <c r="BD10" s="248" t="s">
         <v>73</v>
       </c>
       <c r="BE10" s="250" t="s">
@@ -8429,10 +8429,10 @@
       <c r="BG10" s="250" t="s">
         <v>76</v>
       </c>
-      <c r="BH10" s="269" t="s">
+      <c r="BH10" s="248" t="s">
         <v>77</v>
       </c>
-      <c r="BI10" s="269" t="s">
+      <c r="BI10" s="248" t="s">
         <v>78</v>
       </c>
       <c r="BJ10" s="250" t="s">
@@ -8441,37 +8441,37 @@
       <c r="BK10" s="250" t="s">
         <v>80</v>
       </c>
-      <c r="BL10" s="247" t="s">
+      <c r="BL10" s="261" t="s">
         <v>81</v>
       </c>
-      <c r="BM10" s="269" t="s">
+      <c r="BM10" s="248" t="s">
         <v>82</v>
       </c>
-      <c r="BN10" s="313" t="s">
+      <c r="BN10" s="267" t="s">
         <v>83</v>
       </c>
-      <c r="BO10" s="269" t="s">
+      <c r="BO10" s="248" t="s">
         <v>84</v>
       </c>
-      <c r="BP10" s="313" t="s">
+      <c r="BP10" s="267" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="313" t="s">
+      <c r="BQ10" s="267" t="s">
         <v>86</v>
       </c>
-      <c r="BR10" s="248"/>
-      <c r="BS10" s="248"/>
-      <c r="BT10" s="248"/>
-      <c r="BU10" s="265"/>
+      <c r="BR10" s="262"/>
+      <c r="BS10" s="262"/>
+      <c r="BT10" s="262"/>
+      <c r="BU10" s="253"/>
       <c r="BV10" s="220"/>
-      <c r="BW10" s="254"/>
-      <c r="BX10" s="261"/>
-      <c r="BY10" s="262"/>
-      <c r="BZ10" s="262"/>
-      <c r="CA10" s="263"/>
-      <c r="CB10" s="246"/>
-      <c r="CC10" s="246"/>
-      <c r="CD10" s="246"/>
+      <c r="BW10" s="308"/>
+      <c r="BX10" s="315"/>
+      <c r="BY10" s="316"/>
+      <c r="BZ10" s="316"/>
+      <c r="CA10" s="317"/>
+      <c r="CB10" s="305"/>
+      <c r="CC10" s="305"/>
+      <c r="CD10" s="305"/>
       <c r="CE10" s="219" t="s">
         <v>3</v>
       </c>
@@ -8479,60 +8479,60 @@
       <c r="CI10" s="135"/>
     </row>
     <row r="11" spans="1:87" s="136" customFormat="1" ht="42">
-      <c r="A11" s="297"/>
-      <c r="B11" s="300"/>
-      <c r="C11" s="249"/>
-      <c r="D11" s="303"/>
-      <c r="E11" s="303"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="306"/>
-      <c r="H11" s="274"/>
-      <c r="I11" s="274"/>
-      <c r="J11" s="306"/>
-      <c r="K11" s="282"/>
-      <c r="L11" s="282"/>
-      <c r="M11" s="282"/>
-      <c r="N11" s="282"/>
-      <c r="O11" s="282"/>
-      <c r="P11" s="282"/>
-      <c r="Q11" s="282"/>
-      <c r="R11" s="282"/>
-      <c r="S11" s="282"/>
-      <c r="T11" s="282"/>
-      <c r="U11" s="282"/>
+      <c r="A11" s="278"/>
+      <c r="B11" s="281"/>
+      <c r="C11" s="263"/>
+      <c r="D11" s="273"/>
+      <c r="E11" s="273"/>
+      <c r="F11" s="263"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="290"/>
+      <c r="I11" s="290"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="247"/>
+      <c r="L11" s="247"/>
+      <c r="M11" s="247"/>
+      <c r="N11" s="247"/>
+      <c r="O11" s="247"/>
+      <c r="P11" s="247"/>
+      <c r="Q11" s="247"/>
+      <c r="R11" s="247"/>
+      <c r="S11" s="247"/>
+      <c r="T11" s="247"/>
+      <c r="U11" s="247"/>
       <c r="V11" s="222" t="s">
         <v>87</v>
       </c>
       <c r="W11" s="222" t="s">
         <v>88</v>
       </c>
-      <c r="X11" s="282"/>
-      <c r="Y11" s="285"/>
-      <c r="Z11" s="285"/>
-      <c r="AA11" s="285"/>
-      <c r="AB11" s="285"/>
-      <c r="AC11" s="285"/>
-      <c r="AD11" s="285"/>
-      <c r="AE11" s="285"/>
-      <c r="AF11" s="285"/>
-      <c r="AG11" s="285"/>
-      <c r="AH11" s="285"/>
-      <c r="AI11" s="285"/>
-      <c r="AJ11" s="292"/>
-      <c r="AK11" s="266"/>
-      <c r="AL11" s="314"/>
-      <c r="AM11" s="285"/>
-      <c r="AN11" s="249"/>
-      <c r="AO11" s="249"/>
-      <c r="AP11" s="306"/>
-      <c r="AQ11" s="306"/>
-      <c r="AR11" s="306"/>
-      <c r="AS11" s="306"/>
-      <c r="AT11" s="306"/>
-      <c r="AU11" s="306"/>
-      <c r="AV11" s="249"/>
-      <c r="AW11" s="314"/>
-      <c r="AX11" s="249"/>
+      <c r="X11" s="247"/>
+      <c r="Y11" s="257"/>
+      <c r="Z11" s="257"/>
+      <c r="AA11" s="257"/>
+      <c r="AB11" s="257"/>
+      <c r="AC11" s="257"/>
+      <c r="AD11" s="257"/>
+      <c r="AE11" s="257"/>
+      <c r="AF11" s="257"/>
+      <c r="AG11" s="257"/>
+      <c r="AH11" s="257"/>
+      <c r="AI11" s="257"/>
+      <c r="AJ11" s="302"/>
+      <c r="AK11" s="254"/>
+      <c r="AL11" s="269"/>
+      <c r="AM11" s="257"/>
+      <c r="AN11" s="263"/>
+      <c r="AO11" s="263"/>
+      <c r="AP11" s="260"/>
+      <c r="AQ11" s="260"/>
+      <c r="AR11" s="260"/>
+      <c r="AS11" s="260"/>
+      <c r="AT11" s="260"/>
+      <c r="AU11" s="260"/>
+      <c r="AV11" s="263"/>
+      <c r="AW11" s="269"/>
+      <c r="AX11" s="263"/>
       <c r="AY11" s="226" t="s">
         <v>89</v>
       </c>
@@ -8542,28 +8542,28 @@
       <c r="BA11" s="226" t="s">
         <v>91</v>
       </c>
-      <c r="BB11" s="268"/>
-      <c r="BC11" s="270"/>
-      <c r="BD11" s="270"/>
+      <c r="BB11" s="319"/>
+      <c r="BC11" s="249"/>
+      <c r="BD11" s="249"/>
       <c r="BE11" s="251"/>
       <c r="BF11" s="251"/>
       <c r="BG11" s="251"/>
-      <c r="BH11" s="270"/>
-      <c r="BI11" s="270"/>
+      <c r="BH11" s="249"/>
+      <c r="BI11" s="249"/>
       <c r="BJ11" s="251"/>
       <c r="BK11" s="251"/>
-      <c r="BL11" s="249"/>
-      <c r="BM11" s="270"/>
-      <c r="BN11" s="314"/>
-      <c r="BO11" s="270"/>
-      <c r="BP11" s="314"/>
-      <c r="BQ11" s="314"/>
-      <c r="BR11" s="249"/>
-      <c r="BS11" s="249"/>
-      <c r="BT11" s="249"/>
-      <c r="BU11" s="266"/>
+      <c r="BL11" s="263"/>
+      <c r="BM11" s="249"/>
+      <c r="BN11" s="269"/>
+      <c r="BO11" s="249"/>
+      <c r="BP11" s="269"/>
+      <c r="BQ11" s="269"/>
+      <c r="BR11" s="263"/>
+      <c r="BS11" s="263"/>
+      <c r="BT11" s="263"/>
+      <c r="BU11" s="254"/>
       <c r="BV11" s="220"/>
-      <c r="BW11" s="254"/>
+      <c r="BW11" s="308"/>
       <c r="BX11" s="224" t="s">
         <v>92</v>
       </c>
@@ -8576,9 +8576,9 @@
       <c r="CA11" s="223" t="s">
         <v>95</v>
       </c>
-      <c r="CB11" s="246"/>
-      <c r="CC11" s="246"/>
-      <c r="CD11" s="246"/>
+      <c r="CB11" s="305"/>
+      <c r="CC11" s="305"/>
+      <c r="CD11" s="305"/>
       <c r="CE11" s="225">
         <v>26</v>
       </c>
@@ -8950,8 +8950,9 @@
         <v>61000000</v>
       </c>
       <c r="AW13" s="232"/>
-      <c r="AX13" s="232" t="s">
-        <v>102</v>
+      <c r="AX13" s="232" t="str">
+        <f t="shared" ref="AX13:AX19" si="10">IF(E13="CT","x",0)</f>
+        <v>x</v>
       </c>
       <c r="AY13" s="235">
         <f>ROUND(IF($AX13="x",($G13+$H13)*AY$11,0),0)</f>
@@ -8962,7 +8963,7 @@
         <v>142800</v>
       </c>
       <c r="BA13" s="235">
-        <f t="shared" ref="BA13" si="10">ROUND(IF($AX13="x",($G13+$H13)*BA$11,0),0)</f>
+        <f t="shared" ref="BA13" si="11">ROUND(IF($AX13="x",($G13+$H13)*BA$11,0),0)</f>
         <v>95200</v>
       </c>
       <c r="BB13" s="235">
@@ -8990,7 +8991,7 @@
         <v>4400000</v>
       </c>
       <c r="BJ13" s="235">
-        <f t="shared" ref="BJ13:BJ19" si="11">IF(E13="CT",11000000,0)</f>
+        <f t="shared" ref="BJ13:BJ19" si="12">IF(E13="CT",11000000,0)</f>
         <v>11000000</v>
       </c>
       <c r="BK13" s="235">
@@ -9071,7 +9072,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" ref="I14:I19" si="12">CB14-BZ14-G14-H14</f>
+        <f t="shared" ref="I14:I19" si="13">CB14-BZ14-G14-H14</f>
         <v>43520000</v>
       </c>
       <c r="J14" s="152">
@@ -9122,27 +9123,27 @@
         <v>7827692.307692308</v>
       </c>
       <c r="Z14" s="14">
-        <f t="shared" ref="Z14:Z15" si="13">M14*G14/26</f>
+        <f t="shared" ref="Z14:Z15" si="14">M14*G14/26</f>
         <v>0</v>
       </c>
       <c r="AA14" s="14">
-        <f t="shared" ref="AA14:AA15" si="14">G14*N14/26</f>
+        <f t="shared" ref="AA14:AA15" si="15">G14*N14/26</f>
         <v>0</v>
       </c>
       <c r="AB14" s="14">
-        <f t="shared" ref="AB14:AB15" si="15">G14*O14/26</f>
+        <f t="shared" ref="AB14:AB15" si="16">G14*O14/26</f>
         <v>0</v>
       </c>
       <c r="AC14" s="14">
-        <f t="shared" ref="AC14:AC15" si="16">G14*P14*150%/26</f>
+        <f t="shared" ref="AC14:AC15" si="17">G14*P14*150%/26</f>
         <v>0</v>
       </c>
       <c r="AD14" s="14">
-        <f t="shared" ref="AD14:AD15" si="17">G14*Q14/26*200%</f>
+        <f t="shared" ref="AD14:AD15" si="18">G14*Q14/26*200%</f>
         <v>0</v>
       </c>
       <c r="AE14" s="14">
-        <f t="shared" ref="AE14:AE15" si="18">G14*R14/26*300%</f>
+        <f t="shared" ref="AE14:AE15" si="19">G14*R14/26*300%</f>
         <v>0</v>
       </c>
       <c r="AF14" s="14">
@@ -9150,7 +9151,7 @@
         <v>0</v>
       </c>
       <c r="AG14" s="14">
-        <f t="shared" ref="AG14:AG15" si="19">T14*G14/26/8</f>
+        <f t="shared" ref="AG14:AG15" si="20">T14*G14/26/8</f>
         <v>0</v>
       </c>
       <c r="AH14" s="14">
@@ -9158,7 +9159,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="14">
-        <f t="shared" ref="AI14:AI15" si="20">G14*V14/26</f>
+        <f t="shared" ref="AI14:AI15" si="21">G14*V14/26</f>
         <v>0</v>
       </c>
       <c r="AJ14" s="14"/>
@@ -9172,7 +9173,7 @@
         <v>0</v>
       </c>
       <c r="AN14" s="14">
-        <f t="shared" ref="AN14:AN15" si="21">H14/26*K14</f>
+        <f t="shared" ref="AN14:AN15" si="22">H14/26*K14</f>
         <v>0</v>
       </c>
       <c r="AO14" s="14">
@@ -9188,12 +9189,12 @@
       <c r="AT14" s="14"/>
       <c r="AU14" s="14"/>
       <c r="AV14" s="14">
-        <f t="shared" ref="AV14:AV15" si="22">Y14+Z14+AA14+AB14+AC14+AD14+AE14+AF14+AG14+AI14+AJ14+AK14+AL14+AM14+AN14+AO14+AP14-AQ14+AR14+AS14+AT14+AU14</f>
+        <f t="shared" ref="AV14:AV15" si="23">Y14+Z14+AA14+AB14+AC14+AD14+AE14+AF14+AG14+AI14+AJ14+AK14+AL14+AM14+AN14+AO14+AP14-AQ14+AR14+AS14+AT14+AU14</f>
         <v>48758461.538461544</v>
       </c>
       <c r="AW14" s="14"/>
       <c r="AX14" s="14" t="str">
-        <f t="shared" ref="AX14:AX19" si="23">IF(E14="CT","x",0)</f>
+        <f t="shared" si="10"/>
         <v>x</v>
       </c>
       <c r="AY14" s="13">
@@ -9231,7 +9232,7 @@
         <v>4400000</v>
       </c>
       <c r="BJ14" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11000000</v>
       </c>
       <c r="BK14" s="13">
@@ -9315,7 +9316,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>34180000</v>
       </c>
       <c r="J15" s="152">
@@ -9366,27 +9367,27 @@
         <v>7218461.538461538</v>
       </c>
       <c r="Z15" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA15" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AB15" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AC15" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD15" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AE15" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AF15" s="14">
@@ -9394,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="AG15" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AH15" s="14">
@@ -9402,7 +9403,7 @@
         <v>3246153.846153846</v>
       </c>
       <c r="AI15" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AJ15" s="14"/>
@@ -9416,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="AN15" s="14">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AO15" s="14">
@@ -9432,12 +9433,12 @@
       <c r="AT15" s="14"/>
       <c r="AU15" s="14"/>
       <c r="AV15" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>42575384.615384616</v>
       </c>
       <c r="AW15" s="14"/>
       <c r="AX15" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="10"/>
         <v>x</v>
       </c>
       <c r="AY15" s="13">
@@ -9475,7 +9476,7 @@
         <v>4400000</v>
       </c>
       <c r="BJ15" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11000000</v>
       </c>
       <c r="BK15" s="13">
@@ -9559,7 +9560,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>19160000</v>
       </c>
       <c r="J16" s="152">
@@ -9681,7 +9682,7 @@
       </c>
       <c r="AW16" s="14"/>
       <c r="AX16" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="10"/>
         <v>x</v>
       </c>
       <c r="AY16" s="13">
@@ -9719,7 +9720,7 @@
         <v>4400000</v>
       </c>
       <c r="BJ16" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11000000</v>
       </c>
       <c r="BK16" s="13">
@@ -9803,7 +9804,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6700000</v>
       </c>
       <c r="J17" s="152">
@@ -9925,7 +9926,7 @@
       </c>
       <c r="AW17" s="14"/>
       <c r="AX17" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="10"/>
         <v>x</v>
       </c>
       <c r="AY17" s="13">
@@ -9963,7 +9964,7 @@
         <v>4400000</v>
       </c>
       <c r="BJ17" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11000000</v>
       </c>
       <c r="BK17" s="13">
@@ -10047,7 +10048,7 @@
         <v>780000</v>
       </c>
       <c r="I18" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>17030000</v>
       </c>
       <c r="J18" s="152">
@@ -10169,7 +10170,7 @@
       </c>
       <c r="AW18" s="14"/>
       <c r="AX18" s="14">
-        <f t="shared" si="23"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY18" s="13">
@@ -10207,7 +10208,7 @@
         <v>4400000</v>
       </c>
       <c r="BJ18" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BK18" s="13">
@@ -10293,7 +10294,7 @@
         <v>300000</v>
       </c>
       <c r="I19" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11210000</v>
       </c>
       <c r="J19" s="152">
@@ -10415,7 +10416,7 @@
       </c>
       <c r="AW19" s="14"/>
       <c r="AX19" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="10"/>
         <v>x</v>
       </c>
       <c r="AY19" s="13">
@@ -10453,7 +10454,7 @@
         <v>4400000</v>
       </c>
       <c r="BJ19" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11000000</v>
       </c>
       <c r="BK19" s="13">
@@ -10645,24 +10646,54 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="82">
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="AY8:BQ8"/>
-    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="BW8:BW11"/>
+    <mergeCell ref="BX8:CA10"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="BR8:BS8"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="AY9:BL9"/>
+    <mergeCell ref="BM9:BQ9"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BQ10:BQ11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="A3:BU3"/>
     <mergeCell ref="BJ10:BJ11"/>
     <mergeCell ref="AN9:AN11"/>
@@ -10679,54 +10710,24 @@
     <mergeCell ref="BO10:BO11"/>
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="E8:E11"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="AY9:BL9"/>
-    <mergeCell ref="BM9:BQ9"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BQ10:BQ11"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="BX8:CA10"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BR8:BS8"/>
-    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AI9:AI11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="AY8:BQ8"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="BH10:BH11"/>
   </mergeCells>
   <conditionalFormatting sqref="B13:B1048576 B1:B11">
     <cfRule type="duplicateValues" dxfId="22" priority="36"/>
@@ -10934,91 +10935,91 @@
       <c r="CD2" s="30"/>
     </row>
     <row r="3" spans="1:87" s="32" customFormat="1" outlineLevel="1">
-      <c r="A3" s="367" t="str">
+      <c r="A3" s="321" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
         <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
       </c>
-      <c r="B3" s="367"/>
-      <c r="C3" s="367"/>
-      <c r="D3" s="367"/>
-      <c r="E3" s="367"/>
-      <c r="F3" s="367"/>
-      <c r="G3" s="367"/>
-      <c r="H3" s="367"/>
-      <c r="I3" s="367"/>
-      <c r="J3" s="367"/>
-      <c r="K3" s="367"/>
-      <c r="L3" s="367"/>
-      <c r="M3" s="367"/>
-      <c r="N3" s="367"/>
-      <c r="O3" s="367"/>
-      <c r="P3" s="367"/>
-      <c r="Q3" s="367"/>
-      <c r="R3" s="367"/>
-      <c r="S3" s="367"/>
-      <c r="T3" s="367"/>
-      <c r="U3" s="367"/>
-      <c r="V3" s="367"/>
-      <c r="W3" s="367"/>
-      <c r="X3" s="367"/>
-      <c r="Y3" s="367"/>
-      <c r="Z3" s="367"/>
-      <c r="AA3" s="367"/>
-      <c r="AB3" s="367"/>
-      <c r="AC3" s="367"/>
-      <c r="AD3" s="367"/>
-      <c r="AE3" s="367"/>
-      <c r="AF3" s="367"/>
-      <c r="AG3" s="367"/>
-      <c r="AH3" s="367"/>
-      <c r="AI3" s="367"/>
-      <c r="AJ3" s="367"/>
-      <c r="AK3" s="367"/>
-      <c r="AL3" s="367"/>
-      <c r="AM3" s="367"/>
-      <c r="AN3" s="367"/>
-      <c r="AO3" s="367"/>
-      <c r="AP3" s="367"/>
-      <c r="AQ3" s="367"/>
-      <c r="AR3" s="367"/>
-      <c r="AS3" s="367"/>
-      <c r="AT3" s="367"/>
-      <c r="AU3" s="367"/>
-      <c r="AV3" s="367"/>
-      <c r="AW3" s="367"/>
-      <c r="AX3" s="367"/>
-      <c r="AY3" s="367"/>
-      <c r="AZ3" s="367"/>
-      <c r="BA3" s="367"/>
-      <c r="BB3" s="367"/>
-      <c r="BC3" s="367"/>
-      <c r="BD3" s="367"/>
-      <c r="BE3" s="367"/>
-      <c r="BF3" s="367"/>
-      <c r="BG3" s="367"/>
-      <c r="BH3" s="367"/>
-      <c r="BI3" s="367"/>
-      <c r="BJ3" s="367"/>
-      <c r="BK3" s="367"/>
-      <c r="BL3" s="367"/>
-      <c r="BM3" s="367"/>
-      <c r="BN3" s="367"/>
-      <c r="BO3" s="367"/>
-      <c r="BP3" s="367"/>
-      <c r="BQ3" s="367"/>
-      <c r="BR3" s="367"/>
-      <c r="BS3" s="367"/>
-      <c r="BT3" s="367"/>
-      <c r="BU3" s="367"/>
+      <c r="B3" s="321"/>
+      <c r="C3" s="321"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="321"/>
+      <c r="F3" s="321"/>
+      <c r="G3" s="321"/>
+      <c r="H3" s="321"/>
+      <c r="I3" s="321"/>
+      <c r="J3" s="321"/>
+      <c r="K3" s="321"/>
+      <c r="L3" s="321"/>
+      <c r="M3" s="321"/>
+      <c r="N3" s="321"/>
+      <c r="O3" s="321"/>
+      <c r="P3" s="321"/>
+      <c r="Q3" s="321"/>
+      <c r="R3" s="321"/>
+      <c r="S3" s="321"/>
+      <c r="T3" s="321"/>
+      <c r="U3" s="321"/>
+      <c r="V3" s="321"/>
+      <c r="W3" s="321"/>
+      <c r="X3" s="321"/>
+      <c r="Y3" s="321"/>
+      <c r="Z3" s="321"/>
+      <c r="AA3" s="321"/>
+      <c r="AB3" s="321"/>
+      <c r="AC3" s="321"/>
+      <c r="AD3" s="321"/>
+      <c r="AE3" s="321"/>
+      <c r="AF3" s="321"/>
+      <c r="AG3" s="321"/>
+      <c r="AH3" s="321"/>
+      <c r="AI3" s="321"/>
+      <c r="AJ3" s="321"/>
+      <c r="AK3" s="321"/>
+      <c r="AL3" s="321"/>
+      <c r="AM3" s="321"/>
+      <c r="AN3" s="321"/>
+      <c r="AO3" s="321"/>
+      <c r="AP3" s="321"/>
+      <c r="AQ3" s="321"/>
+      <c r="AR3" s="321"/>
+      <c r="AS3" s="321"/>
+      <c r="AT3" s="321"/>
+      <c r="AU3" s="321"/>
+      <c r="AV3" s="321"/>
+      <c r="AW3" s="321"/>
+      <c r="AX3" s="321"/>
+      <c r="AY3" s="321"/>
+      <c r="AZ3" s="321"/>
+      <c r="BA3" s="321"/>
+      <c r="BB3" s="321"/>
+      <c r="BC3" s="321"/>
+      <c r="BD3" s="321"/>
+      <c r="BE3" s="321"/>
+      <c r="BF3" s="321"/>
+      <c r="BG3" s="321"/>
+      <c r="BH3" s="321"/>
+      <c r="BI3" s="321"/>
+      <c r="BJ3" s="321"/>
+      <c r="BK3" s="321"/>
+      <c r="BL3" s="321"/>
+      <c r="BM3" s="321"/>
+      <c r="BN3" s="321"/>
+      <c r="BO3" s="321"/>
+      <c r="BP3" s="321"/>
+      <c r="BQ3" s="321"/>
+      <c r="BR3" s="321"/>
+      <c r="BS3" s="321"/>
+      <c r="BT3" s="321"/>
+      <c r="BU3" s="321"/>
       <c r="BV3"/>
-      <c r="BW3" s="368" t="s">
+      <c r="BW3" s="322" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="368"/>
-      <c r="BY3" s="368"/>
-      <c r="BZ3" s="368"/>
-      <c r="CA3" s="368"/>
-      <c r="CB3" s="367"/>
+      <c r="BX3" s="322"/>
+      <c r="BY3" s="322"/>
+      <c r="BZ3" s="322"/>
+      <c r="CA3" s="322"/>
+      <c r="CB3" s="321"/>
       <c r="CC3" s="31"/>
       <c r="CD3" s="31"/>
       <c r="CE3" s="32" t="s">
@@ -11102,366 +11103,366 @@
       <c r="BT4" s="33"/>
       <c r="BU4" s="33"/>
       <c r="BV4"/>
-      <c r="BW4" s="367"/>
-      <c r="BX4" s="367"/>
-      <c r="BY4" s="367"/>
-      <c r="BZ4" s="367"/>
-      <c r="CA4" s="367"/>
-      <c r="CB4" s="367"/>
+      <c r="BW4" s="321"/>
+      <c r="BX4" s="321"/>
+      <c r="BY4" s="321"/>
+      <c r="BZ4" s="321"/>
+      <c r="CA4" s="321"/>
+      <c r="CB4" s="321"/>
       <c r="CC4" s="31"/>
       <c r="CD4" s="31"/>
     </row>
     <row r="5" spans="1:87" s="34" customFormat="1">
-      <c r="A5" s="369" t="s">
+      <c r="A5" s="323" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="372" t="s">
+      <c r="B5" s="326" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="320" t="s">
+      <c r="C5" s="329" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="375" t="s">
+      <c r="D5" s="332" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="375" t="s">
+      <c r="E5" s="332" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="320" t="s">
+      <c r="F5" s="329" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="320" t="s">
+      <c r="G5" s="329" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="333" t="s">
+      <c r="H5" s="335" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="333" t="s">
+      <c r="I5" s="335" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="320" t="s">
+      <c r="J5" s="329" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="378" t="s">
+      <c r="K5" s="338" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="379"/>
-      <c r="M5" s="379"/>
-      <c r="N5" s="379"/>
-      <c r="O5" s="379"/>
-      <c r="P5" s="379"/>
-      <c r="Q5" s="379"/>
-      <c r="R5" s="379"/>
-      <c r="S5" s="379"/>
-      <c r="T5" s="379"/>
-      <c r="U5" s="379"/>
-      <c r="V5" s="379"/>
-      <c r="W5" s="379"/>
-      <c r="X5" s="379"/>
-      <c r="Y5" s="380" t="s">
+      <c r="L5" s="339"/>
+      <c r="M5" s="339"/>
+      <c r="N5" s="339"/>
+      <c r="O5" s="339"/>
+      <c r="P5" s="339"/>
+      <c r="Q5" s="339"/>
+      <c r="R5" s="339"/>
+      <c r="S5" s="339"/>
+      <c r="T5" s="339"/>
+      <c r="U5" s="339"/>
+      <c r="V5" s="339"/>
+      <c r="W5" s="339"/>
+      <c r="X5" s="339"/>
+      <c r="Y5" s="340" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="381"/>
-      <c r="AA5" s="381"/>
-      <c r="AB5" s="381"/>
-      <c r="AC5" s="381"/>
-      <c r="AD5" s="381"/>
-      <c r="AE5" s="381"/>
-      <c r="AF5" s="381"/>
-      <c r="AG5" s="381"/>
-      <c r="AH5" s="381"/>
-      <c r="AI5" s="381"/>
-      <c r="AJ5" s="381"/>
-      <c r="AK5" s="381"/>
-      <c r="AL5" s="381"/>
-      <c r="AM5" s="381"/>
-      <c r="AN5" s="381"/>
-      <c r="AO5" s="382"/>
-      <c r="AP5" s="320" t="s">
+      <c r="Z5" s="341"/>
+      <c r="AA5" s="341"/>
+      <c r="AB5" s="341"/>
+      <c r="AC5" s="341"/>
+      <c r="AD5" s="341"/>
+      <c r="AE5" s="341"/>
+      <c r="AF5" s="341"/>
+      <c r="AG5" s="341"/>
+      <c r="AH5" s="341"/>
+      <c r="AI5" s="341"/>
+      <c r="AJ5" s="341"/>
+      <c r="AK5" s="341"/>
+      <c r="AL5" s="341"/>
+      <c r="AM5" s="341"/>
+      <c r="AN5" s="341"/>
+      <c r="AO5" s="342"/>
+      <c r="AP5" s="329" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="320" t="s">
+      <c r="AQ5" s="329" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="320" t="s">
+      <c r="AR5" s="329" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="320" t="s">
+      <c r="AS5" s="329" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="320" t="s">
+      <c r="AT5" s="329" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="320" t="s">
+      <c r="AU5" s="329" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="320" t="s">
+      <c r="AV5" s="329" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="320" t="s">
+      <c r="AW5" s="329" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="320" t="s">
+      <c r="AX5" s="329" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="323" t="s">
+      <c r="AY5" s="350" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="324"/>
-      <c r="BA5" s="324"/>
-      <c r="BB5" s="324"/>
-      <c r="BC5" s="324"/>
-      <c r="BD5" s="324"/>
-      <c r="BE5" s="324"/>
-      <c r="BF5" s="324"/>
-      <c r="BG5" s="324"/>
-      <c r="BH5" s="324"/>
-      <c r="BI5" s="324"/>
-      <c r="BJ5" s="324"/>
-      <c r="BK5" s="324"/>
-      <c r="BL5" s="324"/>
-      <c r="BM5" s="324"/>
-      <c r="BN5" s="324"/>
-      <c r="BO5" s="324"/>
-      <c r="BP5" s="324"/>
-      <c r="BQ5" s="325"/>
-      <c r="BR5" s="351" t="s">
+      <c r="AZ5" s="351"/>
+      <c r="BA5" s="351"/>
+      <c r="BB5" s="351"/>
+      <c r="BC5" s="351"/>
+      <c r="BD5" s="351"/>
+      <c r="BE5" s="351"/>
+      <c r="BF5" s="351"/>
+      <c r="BG5" s="351"/>
+      <c r="BH5" s="351"/>
+      <c r="BI5" s="351"/>
+      <c r="BJ5" s="351"/>
+      <c r="BK5" s="351"/>
+      <c r="BL5" s="351"/>
+      <c r="BM5" s="351"/>
+      <c r="BN5" s="351"/>
+      <c r="BO5" s="351"/>
+      <c r="BP5" s="351"/>
+      <c r="BQ5" s="352"/>
+      <c r="BR5" s="353" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="360"/>
-      <c r="BT5" s="328" t="s">
+      <c r="BS5" s="354"/>
+      <c r="BT5" s="355" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="351" t="s">
+      <c r="BU5" s="353" t="s">
         <v>28</v>
       </c>
       <c r="BV5"/>
-      <c r="BW5" s="354" t="s">
+      <c r="BW5" s="376" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="339" t="s">
+      <c r="BX5" s="362" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="340"/>
-      <c r="BZ5" s="340"/>
-      <c r="CA5" s="341"/>
-      <c r="CB5" s="348" t="s">
+      <c r="BY5" s="363"/>
+      <c r="BZ5" s="363"/>
+      <c r="CA5" s="364"/>
+      <c r="CB5" s="371" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="244" t="s">
+      <c r="CC5" s="303" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="244" t="s">
+      <c r="CD5" s="303" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="35"/>
       <c r="CI5" s="36"/>
     </row>
     <row r="6" spans="1:87" s="34" customFormat="1">
-      <c r="A6" s="370"/>
-      <c r="B6" s="373"/>
-      <c r="C6" s="321"/>
-      <c r="D6" s="376"/>
-      <c r="E6" s="376"/>
-      <c r="F6" s="321"/>
-      <c r="G6" s="321"/>
-      <c r="H6" s="334"/>
-      <c r="I6" s="334"/>
-      <c r="J6" s="321"/>
-      <c r="K6" s="357" t="s">
+      <c r="A6" s="324"/>
+      <c r="B6" s="327"/>
+      <c r="C6" s="330"/>
+      <c r="D6" s="333"/>
+      <c r="E6" s="333"/>
+      <c r="F6" s="330"/>
+      <c r="G6" s="330"/>
+      <c r="H6" s="336"/>
+      <c r="I6" s="336"/>
+      <c r="J6" s="330"/>
+      <c r="K6" s="343" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="357" t="s">
+      <c r="L6" s="343" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="357" t="s">
+      <c r="M6" s="343" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="357" t="s">
+      <c r="N6" s="343" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="357" t="s">
+      <c r="O6" s="343" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="357" t="s">
+      <c r="P6" s="343" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="357" t="s">
+      <c r="Q6" s="343" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="357" t="s">
+      <c r="R6" s="343" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="357" t="s">
+      <c r="S6" s="343" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="357" t="s">
+      <c r="T6" s="343" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="357" t="s">
+      <c r="U6" s="343" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="363" t="s">
+      <c r="V6" s="346" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="364"/>
-      <c r="X6" s="357" t="s">
+      <c r="W6" s="347"/>
+      <c r="X6" s="343" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="320" t="s">
+      <c r="Y6" s="329" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="320" t="s">
+      <c r="Z6" s="329" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="320" t="s">
+      <c r="AA6" s="329" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="320" t="s">
+      <c r="AB6" s="329" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="333" t="s">
+      <c r="AC6" s="335" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="333" t="s">
+      <c r="AD6" s="335" t="s">
         <v>52</v>
       </c>
-      <c r="AE6" s="333" t="s">
+      <c r="AE6" s="335" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="333" t="s">
+      <c r="AF6" s="335" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="320" t="s">
+      <c r="AG6" s="329" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="333" t="s">
+      <c r="AH6" s="335" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="333" t="s">
+      <c r="AI6" s="335" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="320" t="s">
+      <c r="AJ6" s="329" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="336" t="s">
+      <c r="AK6" s="379" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="320" t="s">
+      <c r="AL6" s="329" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="320" t="s">
+      <c r="AM6" s="329" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="247" t="s">
+      <c r="AN6" s="261" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="320" t="s">
+      <c r="AO6" s="329" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="321"/>
-      <c r="AQ6" s="321"/>
-      <c r="AR6" s="321"/>
-      <c r="AS6" s="321"/>
-      <c r="AT6" s="321"/>
-      <c r="AU6" s="321"/>
-      <c r="AV6" s="321"/>
-      <c r="AW6" s="321"/>
-      <c r="AX6" s="321"/>
-      <c r="AY6" s="323" t="s">
+      <c r="AP6" s="330"/>
+      <c r="AQ6" s="330"/>
+      <c r="AR6" s="330"/>
+      <c r="AS6" s="330"/>
+      <c r="AT6" s="330"/>
+      <c r="AU6" s="330"/>
+      <c r="AV6" s="330"/>
+      <c r="AW6" s="330"/>
+      <c r="AX6" s="330"/>
+      <c r="AY6" s="350" t="s">
         <v>64</v>
       </c>
-      <c r="AZ6" s="324"/>
-      <c r="BA6" s="324"/>
-      <c r="BB6" s="324"/>
-      <c r="BC6" s="324"/>
-      <c r="BD6" s="324"/>
-      <c r="BE6" s="324"/>
-      <c r="BF6" s="324"/>
-      <c r="BG6" s="324"/>
-      <c r="BH6" s="324"/>
-      <c r="BI6" s="324"/>
-      <c r="BJ6" s="324"/>
-      <c r="BK6" s="324"/>
-      <c r="BL6" s="325"/>
-      <c r="BM6" s="323" t="s">
+      <c r="AZ6" s="351"/>
+      <c r="BA6" s="351"/>
+      <c r="BB6" s="351"/>
+      <c r="BC6" s="351"/>
+      <c r="BD6" s="351"/>
+      <c r="BE6" s="351"/>
+      <c r="BF6" s="351"/>
+      <c r="BG6" s="351"/>
+      <c r="BH6" s="351"/>
+      <c r="BI6" s="351"/>
+      <c r="BJ6" s="351"/>
+      <c r="BK6" s="351"/>
+      <c r="BL6" s="352"/>
+      <c r="BM6" s="350" t="s">
         <v>65</v>
       </c>
-      <c r="BN6" s="324"/>
-      <c r="BO6" s="324"/>
-      <c r="BP6" s="324"/>
-      <c r="BQ6" s="325"/>
-      <c r="BR6" s="326" t="s">
+      <c r="BN6" s="351"/>
+      <c r="BO6" s="351"/>
+      <c r="BP6" s="351"/>
+      <c r="BQ6" s="352"/>
+      <c r="BR6" s="356" t="s">
         <v>66</v>
       </c>
-      <c r="BS6" s="326" t="s">
+      <c r="BS6" s="356" t="s">
         <v>67</v>
       </c>
-      <c r="BT6" s="326"/>
-      <c r="BU6" s="352"/>
+      <c r="BT6" s="356"/>
+      <c r="BU6" s="374"/>
       <c r="BV6"/>
-      <c r="BW6" s="355"/>
-      <c r="BX6" s="342"/>
-      <c r="BY6" s="343"/>
-      <c r="BZ6" s="343"/>
-      <c r="CA6" s="344"/>
-      <c r="CB6" s="349"/>
-      <c r="CC6" s="245"/>
-      <c r="CD6" s="245"/>
+      <c r="BW6" s="377"/>
+      <c r="BX6" s="365"/>
+      <c r="BY6" s="366"/>
+      <c r="BZ6" s="366"/>
+      <c r="CA6" s="367"/>
+      <c r="CB6" s="372"/>
+      <c r="CC6" s="304"/>
+      <c r="CD6" s="304"/>
       <c r="CH6" s="35"/>
       <c r="CI6" s="36"/>
     </row>
     <row r="7" spans="1:87" s="37" customFormat="1">
-      <c r="A7" s="370"/>
-      <c r="B7" s="373"/>
-      <c r="C7" s="321"/>
-      <c r="D7" s="376"/>
-      <c r="E7" s="376"/>
-      <c r="F7" s="321"/>
-      <c r="G7" s="321"/>
-      <c r="H7" s="334"/>
-      <c r="I7" s="334"/>
-      <c r="J7" s="321"/>
-      <c r="K7" s="358"/>
-      <c r="L7" s="358"/>
-      <c r="M7" s="358"/>
-      <c r="N7" s="358"/>
-      <c r="O7" s="358"/>
-      <c r="P7" s="358"/>
-      <c r="Q7" s="358"/>
-      <c r="R7" s="358"/>
-      <c r="S7" s="358"/>
-      <c r="T7" s="358"/>
-      <c r="U7" s="358"/>
-      <c r="V7" s="365"/>
-      <c r="W7" s="366"/>
-      <c r="X7" s="358"/>
-      <c r="Y7" s="321"/>
-      <c r="Z7" s="321"/>
-      <c r="AA7" s="321"/>
-      <c r="AB7" s="321"/>
-      <c r="AC7" s="334"/>
-      <c r="AD7" s="334"/>
-      <c r="AE7" s="334"/>
-      <c r="AF7" s="334"/>
-      <c r="AG7" s="321"/>
-      <c r="AH7" s="334"/>
-      <c r="AI7" s="334"/>
-      <c r="AJ7" s="321"/>
-      <c r="AK7" s="337"/>
-      <c r="AL7" s="321"/>
-      <c r="AM7" s="321"/>
-      <c r="AN7" s="248"/>
-      <c r="AO7" s="321"/>
-      <c r="AP7" s="321"/>
-      <c r="AQ7" s="321"/>
-      <c r="AR7" s="321"/>
-      <c r="AS7" s="321"/>
-      <c r="AT7" s="321"/>
-      <c r="AU7" s="321"/>
-      <c r="AV7" s="321"/>
-      <c r="AW7" s="321"/>
-      <c r="AX7" s="321"/>
+      <c r="A7" s="324"/>
+      <c r="B7" s="327"/>
+      <c r="C7" s="330"/>
+      <c r="D7" s="333"/>
+      <c r="E7" s="333"/>
+      <c r="F7" s="330"/>
+      <c r="G7" s="330"/>
+      <c r="H7" s="336"/>
+      <c r="I7" s="336"/>
+      <c r="J7" s="330"/>
+      <c r="K7" s="344"/>
+      <c r="L7" s="344"/>
+      <c r="M7" s="344"/>
+      <c r="N7" s="344"/>
+      <c r="O7" s="344"/>
+      <c r="P7" s="344"/>
+      <c r="Q7" s="344"/>
+      <c r="R7" s="344"/>
+      <c r="S7" s="344"/>
+      <c r="T7" s="344"/>
+      <c r="U7" s="344"/>
+      <c r="V7" s="348"/>
+      <c r="W7" s="349"/>
+      <c r="X7" s="344"/>
+      <c r="Y7" s="330"/>
+      <c r="Z7" s="330"/>
+      <c r="AA7" s="330"/>
+      <c r="AB7" s="330"/>
+      <c r="AC7" s="336"/>
+      <c r="AD7" s="336"/>
+      <c r="AE7" s="336"/>
+      <c r="AF7" s="336"/>
+      <c r="AG7" s="330"/>
+      <c r="AH7" s="336"/>
+      <c r="AI7" s="336"/>
+      <c r="AJ7" s="330"/>
+      <c r="AK7" s="380"/>
+      <c r="AL7" s="330"/>
+      <c r="AM7" s="330"/>
+      <c r="AN7" s="262"/>
+      <c r="AO7" s="330"/>
+      <c r="AP7" s="330"/>
+      <c r="AQ7" s="330"/>
+      <c r="AR7" s="330"/>
+      <c r="AS7" s="330"/>
+      <c r="AT7" s="330"/>
+      <c r="AU7" s="330"/>
+      <c r="AV7" s="330"/>
+      <c r="AW7" s="330"/>
+      <c r="AX7" s="330"/>
       <c r="AY7" s="16" t="s">
         <v>68</v>
       </c>
@@ -11471,125 +11472,125 @@
       <c r="BA7" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="BB7" s="328" t="s">
+      <c r="BB7" s="355" t="s">
         <v>71</v>
       </c>
-      <c r="BC7" s="329" t="s">
+      <c r="BC7" s="358" t="s">
         <v>72</v>
       </c>
-      <c r="BD7" s="329" t="s">
+      <c r="BD7" s="358" t="s">
         <v>73</v>
       </c>
-      <c r="BE7" s="361" t="s">
+      <c r="BE7" s="360" t="s">
         <v>74</v>
       </c>
-      <c r="BF7" s="329" t="s">
+      <c r="BF7" s="358" t="s">
         <v>75</v>
       </c>
-      <c r="BG7" s="329" t="s">
+      <c r="BG7" s="358" t="s">
         <v>76</v>
       </c>
-      <c r="BH7" s="329" t="s">
+      <c r="BH7" s="358" t="s">
         <v>77</v>
       </c>
-      <c r="BI7" s="329" t="s">
+      <c r="BI7" s="358" t="s">
         <v>78</v>
       </c>
-      <c r="BJ7" s="329" t="s">
+      <c r="BJ7" s="358" t="s">
         <v>79</v>
       </c>
-      <c r="BK7" s="329" t="s">
+      <c r="BK7" s="358" t="s">
         <v>80</v>
       </c>
-      <c r="BL7" s="331" t="s">
+      <c r="BL7" s="382" t="s">
         <v>81</v>
       </c>
-      <c r="BM7" s="329" t="s">
+      <c r="BM7" s="358" t="s">
         <v>82</v>
       </c>
-      <c r="BN7" s="328" t="s">
+      <c r="BN7" s="355" t="s">
         <v>83</v>
       </c>
-      <c r="BO7" s="329" t="s">
+      <c r="BO7" s="358" t="s">
         <v>84</v>
       </c>
-      <c r="BP7" s="328" t="s">
+      <c r="BP7" s="355" t="s">
         <v>85</v>
       </c>
-      <c r="BQ7" s="328" t="s">
+      <c r="BQ7" s="355" t="s">
         <v>86</v>
       </c>
-      <c r="BR7" s="326"/>
-      <c r="BS7" s="326"/>
-      <c r="BT7" s="326"/>
-      <c r="BU7" s="352"/>
+      <c r="BR7" s="356"/>
+      <c r="BS7" s="356"/>
+      <c r="BT7" s="356"/>
+      <c r="BU7" s="374"/>
       <c r="BV7"/>
-      <c r="BW7" s="356"/>
-      <c r="BX7" s="345"/>
-      <c r="BY7" s="346"/>
-      <c r="BZ7" s="346"/>
-      <c r="CA7" s="347"/>
-      <c r="CB7" s="350"/>
-      <c r="CC7" s="246"/>
-      <c r="CD7" s="246"/>
+      <c r="BW7" s="378"/>
+      <c r="BX7" s="368"/>
+      <c r="BY7" s="369"/>
+      <c r="BZ7" s="369"/>
+      <c r="CA7" s="370"/>
+      <c r="CB7" s="373"/>
+      <c r="CC7" s="305"/>
+      <c r="CD7" s="305"/>
       <c r="CH7" s="35"/>
       <c r="CI7" s="36"/>
     </row>
     <row r="8" spans="1:87" s="37" customFormat="1">
-      <c r="A8" s="371"/>
-      <c r="B8" s="374"/>
-      <c r="C8" s="322"/>
-      <c r="D8" s="377"/>
-      <c r="E8" s="377"/>
-      <c r="F8" s="322"/>
-      <c r="G8" s="322"/>
-      <c r="H8" s="335"/>
-      <c r="I8" s="335"/>
-      <c r="J8" s="322"/>
-      <c r="K8" s="359"/>
-      <c r="L8" s="359"/>
-      <c r="M8" s="359"/>
-      <c r="N8" s="359"/>
-      <c r="O8" s="359"/>
-      <c r="P8" s="359"/>
-      <c r="Q8" s="359"/>
-      <c r="R8" s="359"/>
-      <c r="S8" s="359"/>
-      <c r="T8" s="359"/>
-      <c r="U8" s="359"/>
+      <c r="A8" s="325"/>
+      <c r="B8" s="328"/>
+      <c r="C8" s="331"/>
+      <c r="D8" s="334"/>
+      <c r="E8" s="334"/>
+      <c r="F8" s="331"/>
+      <c r="G8" s="331"/>
+      <c r="H8" s="337"/>
+      <c r="I8" s="337"/>
+      <c r="J8" s="331"/>
+      <c r="K8" s="345"/>
+      <c r="L8" s="345"/>
+      <c r="M8" s="345"/>
+      <c r="N8" s="345"/>
+      <c r="O8" s="345"/>
+      <c r="P8" s="345"/>
+      <c r="Q8" s="345"/>
+      <c r="R8" s="345"/>
+      <c r="S8" s="345"/>
+      <c r="T8" s="345"/>
+      <c r="U8" s="345"/>
       <c r="V8" s="38" t="s">
         <v>87</v>
       </c>
       <c r="W8" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="X8" s="359"/>
-      <c r="Y8" s="322"/>
-      <c r="Z8" s="322"/>
-      <c r="AA8" s="322"/>
-      <c r="AB8" s="322"/>
-      <c r="AC8" s="335"/>
-      <c r="AD8" s="335"/>
-      <c r="AE8" s="335"/>
-      <c r="AF8" s="335"/>
-      <c r="AG8" s="322"/>
-      <c r="AH8" s="335"/>
-      <c r="AI8" s="335"/>
-      <c r="AJ8" s="322"/>
-      <c r="AK8" s="338"/>
-      <c r="AL8" s="322"/>
-      <c r="AM8" s="322"/>
-      <c r="AN8" s="249"/>
-      <c r="AO8" s="322"/>
-      <c r="AP8" s="322"/>
-      <c r="AQ8" s="322"/>
-      <c r="AR8" s="322"/>
-      <c r="AS8" s="322"/>
-      <c r="AT8" s="322"/>
-      <c r="AU8" s="322"/>
-      <c r="AV8" s="322"/>
-      <c r="AW8" s="322"/>
-      <c r="AX8" s="322"/>
+      <c r="X8" s="345"/>
+      <c r="Y8" s="331"/>
+      <c r="Z8" s="331"/>
+      <c r="AA8" s="331"/>
+      <c r="AB8" s="331"/>
+      <c r="AC8" s="337"/>
+      <c r="AD8" s="337"/>
+      <c r="AE8" s="337"/>
+      <c r="AF8" s="337"/>
+      <c r="AG8" s="331"/>
+      <c r="AH8" s="337"/>
+      <c r="AI8" s="337"/>
+      <c r="AJ8" s="331"/>
+      <c r="AK8" s="381"/>
+      <c r="AL8" s="331"/>
+      <c r="AM8" s="331"/>
+      <c r="AN8" s="263"/>
+      <c r="AO8" s="331"/>
+      <c r="AP8" s="331"/>
+      <c r="AQ8" s="331"/>
+      <c r="AR8" s="331"/>
+      <c r="AS8" s="331"/>
+      <c r="AT8" s="331"/>
+      <c r="AU8" s="331"/>
+      <c r="AV8" s="331"/>
+      <c r="AW8" s="331"/>
+      <c r="AX8" s="331"/>
       <c r="AY8" s="17" t="s">
         <v>89</v>
       </c>
@@ -11599,28 +11600,28 @@
       <c r="BA8" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="BB8" s="327"/>
-      <c r="BC8" s="330"/>
-      <c r="BD8" s="330"/>
-      <c r="BE8" s="362"/>
-      <c r="BF8" s="330"/>
-      <c r="BG8" s="330"/>
-      <c r="BH8" s="330"/>
-      <c r="BI8" s="330"/>
-      <c r="BJ8" s="330"/>
-      <c r="BK8" s="330"/>
-      <c r="BL8" s="332"/>
-      <c r="BM8" s="330"/>
-      <c r="BN8" s="327"/>
-      <c r="BO8" s="330"/>
-      <c r="BP8" s="327"/>
-      <c r="BQ8" s="327"/>
-      <c r="BR8" s="327"/>
-      <c r="BS8" s="327"/>
-      <c r="BT8" s="327"/>
-      <c r="BU8" s="353"/>
+      <c r="BB8" s="357"/>
+      <c r="BC8" s="359"/>
+      <c r="BD8" s="359"/>
+      <c r="BE8" s="361"/>
+      <c r="BF8" s="359"/>
+      <c r="BG8" s="359"/>
+      <c r="BH8" s="359"/>
+      <c r="BI8" s="359"/>
+      <c r="BJ8" s="359"/>
+      <c r="BK8" s="359"/>
+      <c r="BL8" s="383"/>
+      <c r="BM8" s="359"/>
+      <c r="BN8" s="357"/>
+      <c r="BO8" s="359"/>
+      <c r="BP8" s="357"/>
+      <c r="BQ8" s="357"/>
+      <c r="BR8" s="357"/>
+      <c r="BS8" s="357"/>
+      <c r="BT8" s="357"/>
+      <c r="BU8" s="375"/>
       <c r="BV8"/>
-      <c r="BW8" s="356"/>
+      <c r="BW8" s="378"/>
       <c r="BX8" s="8" t="s">
         <v>92</v>
       </c>
@@ -11633,9 +11634,9 @@
       <c r="CA8" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="CB8" s="350"/>
-      <c r="CC8" s="246"/>
-      <c r="CD8" s="246"/>
+      <c r="CB8" s="373"/>
+      <c r="CC8" s="305"/>
+      <c r="CD8" s="305"/>
       <c r="CE8" s="34"/>
       <c r="CF8" s="39"/>
       <c r="CH8" s="35"/>
@@ -14259,6 +14260,72 @@
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="82">
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="AY6:BL6"/>
+    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="BQ7:BQ8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="AY5:BQ5"/>
+    <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="BS6:BS8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="X6:X8"/>
     <mergeCell ref="A3:BU3"/>
     <mergeCell ref="BW3:CB4"/>
     <mergeCell ref="A5:A8"/>
@@ -14275,84 +14342,18 @@
     <mergeCell ref="Y5:AO5"/>
     <mergeCell ref="AP5:AP8"/>
     <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AY5:BQ5"/>
-    <mergeCell ref="BR5:BS5"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="BS6:BS8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="AY6:BL6"/>
-    <mergeCell ref="BM6:BQ6"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="BQ7:BQ8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BO7:BO8"/>
   </mergeCells>
   <conditionalFormatting sqref="B12:B16 B1:B9 C9:BU9 B20:B1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:B16 B1:B9 D10:F10 J10:BK10 BM10:BU10 C9:BU9 B20:B1048576 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="17" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
     <cfRule type="duplicateValues" dxfId="16" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL10">
     <cfRule type="duplicateValues" dxfId="13" priority="4"/>
@@ -14628,12 +14629,12 @@
       <c r="BR3" s="197"/>
       <c r="BS3" s="197"/>
       <c r="BT3" s="197"/>
-      <c r="BU3" s="294"/>
-      <c r="BV3" s="294"/>
-      <c r="BW3" s="294"/>
-      <c r="BX3" s="294"/>
-      <c r="BY3" s="294"/>
-      <c r="BZ3" s="294"/>
+      <c r="BU3" s="275"/>
+      <c r="BV3" s="275"/>
+      <c r="BW3" s="275"/>
+      <c r="BX3" s="275"/>
+      <c r="BY3" s="275"/>
+      <c r="BZ3" s="275"/>
       <c r="CA3" s="196"/>
       <c r="CB3" s="196"/>
     </row>
@@ -14708,12 +14709,12 @@
       <c r="BR4" s="197"/>
       <c r="BS4" s="197"/>
       <c r="BT4" s="197"/>
-      <c r="BU4" s="294"/>
-      <c r="BV4" s="294"/>
-      <c r="BW4" s="294"/>
-      <c r="BX4" s="294"/>
-      <c r="BY4" s="294"/>
-      <c r="BZ4" s="294"/>
+      <c r="BU4" s="275"/>
+      <c r="BV4" s="275"/>
+      <c r="BW4" s="275"/>
+      <c r="BX4" s="275"/>
+      <c r="BY4" s="275"/>
+      <c r="BZ4" s="275"/>
       <c r="CA4" s="196"/>
       <c r="CB4" s="196"/>
     </row>
@@ -14788,12 +14789,12 @@
       <c r="BR5" s="199"/>
       <c r="BS5" s="199"/>
       <c r="BT5" s="199"/>
-      <c r="BU5" s="293"/>
-      <c r="BV5" s="293"/>
-      <c r="BW5" s="293"/>
-      <c r="BX5" s="293"/>
-      <c r="BY5" s="293"/>
-      <c r="BZ5" s="294"/>
+      <c r="BU5" s="274"/>
+      <c r="BV5" s="274"/>
+      <c r="BW5" s="274"/>
+      <c r="BX5" s="274"/>
+      <c r="BY5" s="274"/>
+      <c r="BZ5" s="275"/>
       <c r="CA5" s="196"/>
       <c r="CB5" s="196"/>
     </row>
@@ -14878,352 +14879,352 @@
       <c r="CB6" s="149"/>
     </row>
     <row r="7" spans="1:85" s="150" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A7" s="298" t="s">
+      <c r="A7" s="279" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="298" t="s">
+      <c r="B7" s="279" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="247" t="s">
+      <c r="C7" s="261" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="301" t="s">
+      <c r="D7" s="271" t="s">
         <v>142</v>
       </c>
-      <c r="E7" s="301" t="s">
+      <c r="E7" s="271" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="383" t="s">
+      <c r="F7" s="409" t="s">
         <v>143</v>
       </c>
-      <c r="G7" s="304" t="s">
+      <c r="G7" s="258" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="272" t="s">
+      <c r="H7" s="288" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="272" t="s">
+      <c r="I7" s="288" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="304" t="s">
+      <c r="J7" s="258" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="275" t="s">
+      <c r="K7" s="291" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="276"/>
-      <c r="M7" s="276"/>
-      <c r="N7" s="276"/>
-      <c r="O7" s="276"/>
-      <c r="P7" s="276"/>
-      <c r="Q7" s="276"/>
-      <c r="R7" s="276"/>
-      <c r="S7" s="276"/>
-      <c r="T7" s="276"/>
-      <c r="U7" s="276"/>
-      <c r="V7" s="276"/>
-      <c r="W7" s="276"/>
-      <c r="X7" s="276"/>
-      <c r="Y7" s="277" t="s">
+      <c r="L7" s="292"/>
+      <c r="M7" s="292"/>
+      <c r="N7" s="292"/>
+      <c r="O7" s="292"/>
+      <c r="P7" s="292"/>
+      <c r="Q7" s="292"/>
+      <c r="R7" s="292"/>
+      <c r="S7" s="292"/>
+      <c r="T7" s="292"/>
+      <c r="U7" s="292"/>
+      <c r="V7" s="292"/>
+      <c r="W7" s="292"/>
+      <c r="X7" s="292"/>
+      <c r="Y7" s="293" t="s">
         <v>15</v>
       </c>
-      <c r="Z7" s="278"/>
-      <c r="AA7" s="278"/>
-      <c r="AB7" s="278"/>
-      <c r="AC7" s="278"/>
-      <c r="AD7" s="278"/>
-      <c r="AE7" s="278"/>
-      <c r="AF7" s="278"/>
-      <c r="AG7" s="278"/>
-      <c r="AH7" s="278"/>
-      <c r="AI7" s="278"/>
-      <c r="AJ7" s="278"/>
-      <c r="AK7" s="278"/>
-      <c r="AL7" s="278"/>
-      <c r="AM7" s="278"/>
-      <c r="AN7" s="278"/>
-      <c r="AO7" s="279"/>
-      <c r="AP7" s="304" t="s">
+      <c r="Z7" s="294"/>
+      <c r="AA7" s="294"/>
+      <c r="AB7" s="294"/>
+      <c r="AC7" s="294"/>
+      <c r="AD7" s="294"/>
+      <c r="AE7" s="294"/>
+      <c r="AF7" s="294"/>
+      <c r="AG7" s="294"/>
+      <c r="AH7" s="294"/>
+      <c r="AI7" s="294"/>
+      <c r="AJ7" s="294"/>
+      <c r="AK7" s="294"/>
+      <c r="AL7" s="294"/>
+      <c r="AM7" s="294"/>
+      <c r="AN7" s="294"/>
+      <c r="AO7" s="295"/>
+      <c r="AP7" s="258" t="s">
         <v>16</v>
       </c>
-      <c r="AQ7" s="304" t="s">
+      <c r="AQ7" s="258" t="s">
         <v>17</v>
       </c>
-      <c r="AR7" s="304" t="s">
+      <c r="AR7" s="258" t="s">
         <v>18</v>
       </c>
-      <c r="AS7" s="304" t="s">
+      <c r="AS7" s="258" t="s">
         <v>19</v>
       </c>
-      <c r="AT7" s="304" t="s">
+      <c r="AT7" s="258" t="s">
         <v>20</v>
       </c>
-      <c r="AU7" s="304" t="s">
+      <c r="AU7" s="258" t="s">
         <v>21</v>
       </c>
-      <c r="AV7" s="247" t="s">
+      <c r="AV7" s="261" t="s">
         <v>22</v>
       </c>
-      <c r="AW7" s="313" t="s">
+      <c r="AW7" s="267" t="s">
         <v>23</v>
       </c>
-      <c r="AX7" s="247" t="s">
+      <c r="AX7" s="261" t="s">
         <v>24</v>
       </c>
-      <c r="AY7" s="317" t="s">
+      <c r="AY7" s="264" t="s">
         <v>25</v>
       </c>
-      <c r="AZ7" s="318"/>
-      <c r="BA7" s="318"/>
-      <c r="BB7" s="318"/>
-      <c r="BC7" s="318"/>
-      <c r="BD7" s="318"/>
-      <c r="BE7" s="318"/>
-      <c r="BF7" s="318"/>
-      <c r="BG7" s="318"/>
-      <c r="BH7" s="318"/>
-      <c r="BI7" s="318"/>
-      <c r="BJ7" s="318"/>
-      <c r="BK7" s="318"/>
-      <c r="BL7" s="318"/>
-      <c r="BM7" s="318"/>
-      <c r="BN7" s="318"/>
-      <c r="BO7" s="318"/>
-      <c r="BP7" s="319"/>
-      <c r="BQ7" s="412" t="s">
+      <c r="AZ7" s="265"/>
+      <c r="BA7" s="265"/>
+      <c r="BB7" s="265"/>
+      <c r="BC7" s="265"/>
+      <c r="BD7" s="265"/>
+      <c r="BE7" s="265"/>
+      <c r="BF7" s="265"/>
+      <c r="BG7" s="265"/>
+      <c r="BH7" s="265"/>
+      <c r="BI7" s="265"/>
+      <c r="BJ7" s="265"/>
+      <c r="BK7" s="265"/>
+      <c r="BL7" s="265"/>
+      <c r="BM7" s="265"/>
+      <c r="BN7" s="265"/>
+      <c r="BO7" s="265"/>
+      <c r="BP7" s="266"/>
+      <c r="BQ7" s="403" t="s">
         <v>26</v>
       </c>
-      <c r="BR7" s="413"/>
-      <c r="BS7" s="247" t="s">
+      <c r="BR7" s="404"/>
+      <c r="BS7" s="261" t="s">
         <v>144</v>
       </c>
-      <c r="BT7" s="247" t="s">
+      <c r="BT7" s="261" t="s">
         <v>27</v>
       </c>
-      <c r="BU7" s="252" t="s">
+      <c r="BU7" s="306" t="s">
         <v>29</v>
       </c>
-      <c r="BV7" s="392" t="s">
+      <c r="BV7" s="394" t="s">
         <v>30</v>
       </c>
-      <c r="BW7" s="393"/>
-      <c r="BX7" s="393"/>
-      <c r="BY7" s="394"/>
-      <c r="BZ7" s="244" t="s">
+      <c r="BW7" s="395"/>
+      <c r="BX7" s="395"/>
+      <c r="BY7" s="396"/>
+      <c r="BZ7" s="303" t="s">
         <v>31</v>
       </c>
-      <c r="CA7" s="244" t="s">
+      <c r="CA7" s="303" t="s">
         <v>32</v>
       </c>
-      <c r="CB7" s="244" t="s">
+      <c r="CB7" s="303" t="s">
         <v>33</v>
       </c>
       <c r="CF7" s="135"/>
       <c r="CG7" s="135"/>
     </row>
     <row r="8" spans="1:85" s="150" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="299"/>
-      <c r="B8" s="299"/>
-      <c r="C8" s="248"/>
-      <c r="D8" s="302"/>
-      <c r="E8" s="302"/>
-      <c r="F8" s="384"/>
-      <c r="G8" s="305"/>
-      <c r="H8" s="273"/>
-      <c r="I8" s="273"/>
-      <c r="J8" s="305"/>
-      <c r="K8" s="280" t="s">
+      <c r="A8" s="280"/>
+      <c r="B8" s="280"/>
+      <c r="C8" s="262"/>
+      <c r="D8" s="272"/>
+      <c r="E8" s="272"/>
+      <c r="F8" s="410"/>
+      <c r="G8" s="259"/>
+      <c r="H8" s="289"/>
+      <c r="I8" s="289"/>
+      <c r="J8" s="259"/>
+      <c r="K8" s="245" t="s">
         <v>34</v>
       </c>
-      <c r="L8" s="280" t="s">
+      <c r="L8" s="245" t="s">
         <v>35</v>
       </c>
-      <c r="M8" s="280" t="s">
+      <c r="M8" s="245" t="s">
         <v>36</v>
       </c>
-      <c r="N8" s="280" t="s">
+      <c r="N8" s="245" t="s">
         <v>37</v>
       </c>
-      <c r="O8" s="280" t="s">
+      <c r="O8" s="245" t="s">
         <v>38</v>
       </c>
-      <c r="P8" s="280" t="s">
+      <c r="P8" s="245" t="s">
         <v>39</v>
       </c>
-      <c r="Q8" s="280" t="s">
+      <c r="Q8" s="245" t="s">
         <v>40</v>
       </c>
-      <c r="R8" s="280" t="s">
+      <c r="R8" s="245" t="s">
         <v>41</v>
       </c>
-      <c r="S8" s="280" t="s">
+      <c r="S8" s="245" t="s">
         <v>42</v>
       </c>
-      <c r="T8" s="280" t="s">
+      <c r="T8" s="245" t="s">
         <v>43</v>
       </c>
-      <c r="U8" s="280" t="s">
+      <c r="U8" s="245" t="s">
         <v>44</v>
       </c>
-      <c r="V8" s="388" t="s">
+      <c r="V8" s="405" t="s">
         <v>45</v>
       </c>
-      <c r="W8" s="389"/>
-      <c r="X8" s="280" t="s">
+      <c r="W8" s="406"/>
+      <c r="X8" s="245" t="s">
         <v>46</v>
       </c>
-      <c r="Y8" s="283" t="s">
+      <c r="Y8" s="255" t="s">
         <v>47</v>
       </c>
-      <c r="Z8" s="283" t="s">
+      <c r="Z8" s="255" t="s">
         <v>48</v>
       </c>
-      <c r="AA8" s="283" t="s">
+      <c r="AA8" s="255" t="s">
         <v>49</v>
       </c>
-      <c r="AB8" s="283" t="s">
+      <c r="AB8" s="255" t="s">
         <v>50</v>
       </c>
-      <c r="AC8" s="283" t="s">
+      <c r="AC8" s="255" t="s">
         <v>51</v>
       </c>
-      <c r="AD8" s="283" t="s">
+      <c r="AD8" s="255" t="s">
         <v>145</v>
       </c>
-      <c r="AE8" s="283" t="s">
+      <c r="AE8" s="255" t="s">
         <v>53</v>
       </c>
-      <c r="AF8" s="283" t="s">
+      <c r="AF8" s="255" t="s">
         <v>54</v>
       </c>
-      <c r="AG8" s="283" t="s">
+      <c r="AG8" s="255" t="s">
         <v>55</v>
       </c>
-      <c r="AH8" s="283" t="s">
+      <c r="AH8" s="255" t="s">
         <v>56</v>
       </c>
-      <c r="AI8" s="283" t="s">
+      <c r="AI8" s="255" t="s">
         <v>57</v>
       </c>
-      <c r="AJ8" s="290" t="s">
+      <c r="AJ8" s="300" t="s">
         <v>58</v>
       </c>
-      <c r="AK8" s="264" t="s">
+      <c r="AK8" s="252" t="s">
         <v>59</v>
       </c>
-      <c r="AL8" s="313" t="s">
+      <c r="AL8" s="267" t="s">
         <v>60</v>
       </c>
-      <c r="AM8" s="283" t="s">
+      <c r="AM8" s="255" t="s">
         <v>61</v>
       </c>
-      <c r="AN8" s="247" t="s">
+      <c r="AN8" s="261" t="s">
         <v>62</v>
       </c>
-      <c r="AO8" s="247" t="s">
+      <c r="AO8" s="261" t="s">
         <v>63</v>
       </c>
-      <c r="AP8" s="305"/>
-      <c r="AQ8" s="305"/>
-      <c r="AR8" s="305"/>
-      <c r="AS8" s="305"/>
-      <c r="AT8" s="305"/>
-      <c r="AU8" s="305"/>
-      <c r="AV8" s="248"/>
-      <c r="AW8" s="316"/>
-      <c r="AX8" s="248"/>
-      <c r="AY8" s="307" t="s">
+      <c r="AP8" s="259"/>
+      <c r="AQ8" s="259"/>
+      <c r="AR8" s="259"/>
+      <c r="AS8" s="259"/>
+      <c r="AT8" s="259"/>
+      <c r="AU8" s="259"/>
+      <c r="AV8" s="262"/>
+      <c r="AW8" s="268"/>
+      <c r="AX8" s="262"/>
+      <c r="AY8" s="282" t="s">
         <v>64</v>
       </c>
-      <c r="AZ8" s="308"/>
-      <c r="BA8" s="308"/>
-      <c r="BB8" s="308"/>
-      <c r="BC8" s="308"/>
-      <c r="BD8" s="308"/>
-      <c r="BE8" s="308"/>
-      <c r="BF8" s="308"/>
-      <c r="BG8" s="308"/>
-      <c r="BH8" s="308"/>
-      <c r="BI8" s="308"/>
-      <c r="BJ8" s="309"/>
-      <c r="BK8" s="307" t="s">
+      <c r="AZ8" s="283"/>
+      <c r="BA8" s="283"/>
+      <c r="BB8" s="283"/>
+      <c r="BC8" s="283"/>
+      <c r="BD8" s="283"/>
+      <c r="BE8" s="283"/>
+      <c r="BF8" s="283"/>
+      <c r="BG8" s="283"/>
+      <c r="BH8" s="283"/>
+      <c r="BI8" s="283"/>
+      <c r="BJ8" s="284"/>
+      <c r="BK8" s="282" t="s">
         <v>65</v>
       </c>
-      <c r="BL8" s="308"/>
-      <c r="BM8" s="308"/>
-      <c r="BN8" s="308"/>
-      <c r="BO8" s="308"/>
-      <c r="BP8" s="309"/>
-      <c r="BQ8" s="248" t="s">
+      <c r="BL8" s="283"/>
+      <c r="BM8" s="283"/>
+      <c r="BN8" s="283"/>
+      <c r="BO8" s="283"/>
+      <c r="BP8" s="284"/>
+      <c r="BQ8" s="262" t="s">
         <v>66</v>
       </c>
-      <c r="BR8" s="248" t="s">
+      <c r="BR8" s="262" t="s">
         <v>67</v>
       </c>
-      <c r="BS8" s="248"/>
-      <c r="BT8" s="248"/>
-      <c r="BU8" s="253"/>
-      <c r="BV8" s="395"/>
-      <c r="BW8" s="396"/>
-      <c r="BX8" s="396"/>
-      <c r="BY8" s="397"/>
-      <c r="BZ8" s="245"/>
-      <c r="CA8" s="245"/>
-      <c r="CB8" s="245"/>
+      <c r="BS8" s="262"/>
+      <c r="BT8" s="262"/>
+      <c r="BU8" s="307"/>
+      <c r="BV8" s="397"/>
+      <c r="BW8" s="398"/>
+      <c r="BX8" s="398"/>
+      <c r="BY8" s="399"/>
+      <c r="BZ8" s="304"/>
+      <c r="CA8" s="304"/>
+      <c r="CB8" s="304"/>
       <c r="CF8" s="135"/>
       <c r="CG8" s="135"/>
     </row>
     <row r="9" spans="1:85" s="136" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="299"/>
-      <c r="B9" s="299"/>
-      <c r="C9" s="248"/>
-      <c r="D9" s="302"/>
-      <c r="E9" s="302"/>
-      <c r="F9" s="384"/>
-      <c r="G9" s="305"/>
-      <c r="H9" s="273"/>
-      <c r="I9" s="273"/>
-      <c r="J9" s="305"/>
-      <c r="K9" s="281"/>
-      <c r="L9" s="281"/>
-      <c r="M9" s="281"/>
-      <c r="N9" s="281"/>
-      <c r="O9" s="281"/>
-      <c r="P9" s="281"/>
-      <c r="Q9" s="281"/>
-      <c r="R9" s="281"/>
-      <c r="S9" s="281"/>
-      <c r="T9" s="281"/>
-      <c r="U9" s="281"/>
-      <c r="V9" s="390"/>
-      <c r="W9" s="391"/>
-      <c r="X9" s="281"/>
-      <c r="Y9" s="284"/>
-      <c r="Z9" s="284"/>
-      <c r="AA9" s="284"/>
-      <c r="AB9" s="284"/>
-      <c r="AC9" s="284"/>
-      <c r="AD9" s="284"/>
-      <c r="AE9" s="284"/>
-      <c r="AF9" s="284"/>
-      <c r="AG9" s="284"/>
-      <c r="AH9" s="284"/>
-      <c r="AI9" s="284"/>
-      <c r="AJ9" s="291"/>
-      <c r="AK9" s="265"/>
-      <c r="AL9" s="316"/>
-      <c r="AM9" s="284"/>
-      <c r="AN9" s="248"/>
-      <c r="AO9" s="248"/>
-      <c r="AP9" s="305"/>
-      <c r="AQ9" s="305"/>
-      <c r="AR9" s="305"/>
-      <c r="AS9" s="305"/>
-      <c r="AT9" s="305"/>
-      <c r="AU9" s="305"/>
-      <c r="AV9" s="248"/>
-      <c r="AW9" s="316"/>
-      <c r="AX9" s="248"/>
+      <c r="A9" s="280"/>
+      <c r="B9" s="280"/>
+      <c r="C9" s="262"/>
+      <c r="D9" s="272"/>
+      <c r="E9" s="272"/>
+      <c r="F9" s="410"/>
+      <c r="G9" s="259"/>
+      <c r="H9" s="289"/>
+      <c r="I9" s="289"/>
+      <c r="J9" s="259"/>
+      <c r="K9" s="246"/>
+      <c r="L9" s="246"/>
+      <c r="M9" s="246"/>
+      <c r="N9" s="246"/>
+      <c r="O9" s="246"/>
+      <c r="P9" s="246"/>
+      <c r="Q9" s="246"/>
+      <c r="R9" s="246"/>
+      <c r="S9" s="246"/>
+      <c r="T9" s="246"/>
+      <c r="U9" s="246"/>
+      <c r="V9" s="407"/>
+      <c r="W9" s="408"/>
+      <c r="X9" s="246"/>
+      <c r="Y9" s="256"/>
+      <c r="Z9" s="256"/>
+      <c r="AA9" s="256"/>
+      <c r="AB9" s="256"/>
+      <c r="AC9" s="256"/>
+      <c r="AD9" s="256"/>
+      <c r="AE9" s="256"/>
+      <c r="AF9" s="256"/>
+      <c r="AG9" s="256"/>
+      <c r="AH9" s="256"/>
+      <c r="AI9" s="256"/>
+      <c r="AJ9" s="301"/>
+      <c r="AK9" s="253"/>
+      <c r="AL9" s="268"/>
+      <c r="AM9" s="256"/>
+      <c r="AN9" s="262"/>
+      <c r="AO9" s="262"/>
+      <c r="AP9" s="259"/>
+      <c r="AQ9" s="259"/>
+      <c r="AR9" s="259"/>
+      <c r="AS9" s="259"/>
+      <c r="AT9" s="259"/>
+      <c r="AU9" s="259"/>
+      <c r="AV9" s="262"/>
+      <c r="AW9" s="268"/>
+      <c r="AX9" s="262"/>
       <c r="AY9" s="221" t="s">
         <v>68</v>
       </c>
@@ -15233,63 +15234,63 @@
       <c r="BA9" s="221" t="s">
         <v>70</v>
       </c>
-      <c r="BB9" s="407" t="s">
+      <c r="BB9" s="390" t="s">
         <v>71</v>
       </c>
-      <c r="BC9" s="401" t="s">
+      <c r="BC9" s="388" t="s">
         <v>72</v>
       </c>
-      <c r="BD9" s="401" t="s">
+      <c r="BD9" s="388" t="s">
         <v>73</v>
       </c>
-      <c r="BE9" s="386" t="s">
+      <c r="BE9" s="392" t="s">
         <v>146</v>
       </c>
-      <c r="BF9" s="386" t="s">
+      <c r="BF9" s="392" t="s">
         <v>75</v>
       </c>
-      <c r="BG9" s="386" t="s">
+      <c r="BG9" s="392" t="s">
         <v>76</v>
       </c>
-      <c r="BH9" s="401" t="s">
+      <c r="BH9" s="388" t="s">
         <v>77</v>
       </c>
-      <c r="BI9" s="386" t="s">
+      <c r="BI9" s="392" t="s">
         <v>80</v>
       </c>
-      <c r="BJ9" s="405" t="s">
+      <c r="BJ9" s="386" t="s">
         <v>81</v>
       </c>
-      <c r="BK9" s="401" t="s">
+      <c r="BK9" s="388" t="s">
         <v>82</v>
       </c>
-      <c r="BL9" s="403" t="s">
+      <c r="BL9" s="384" t="s">
         <v>83</v>
       </c>
-      <c r="BM9" s="401" t="s">
+      <c r="BM9" s="388" t="s">
         <v>84</v>
       </c>
-      <c r="BN9" s="403" t="s">
+      <c r="BN9" s="384" t="s">
         <v>85</v>
       </c>
-      <c r="BO9" s="403" t="s">
+      <c r="BO9" s="384" t="s">
         <v>147</v>
       </c>
-      <c r="BP9" s="247" t="s">
+      <c r="BP9" s="261" t="s">
         <v>86</v>
       </c>
-      <c r="BQ9" s="248"/>
-      <c r="BR9" s="248"/>
-      <c r="BS9" s="248"/>
-      <c r="BT9" s="248"/>
-      <c r="BU9" s="254"/>
-      <c r="BV9" s="398"/>
-      <c r="BW9" s="399"/>
-      <c r="BX9" s="399"/>
-      <c r="BY9" s="400"/>
-      <c r="BZ9" s="246"/>
-      <c r="CA9" s="246"/>
-      <c r="CB9" s="246"/>
+      <c r="BQ9" s="262"/>
+      <c r="BR9" s="262"/>
+      <c r="BS9" s="262"/>
+      <c r="BT9" s="262"/>
+      <c r="BU9" s="308"/>
+      <c r="BV9" s="400"/>
+      <c r="BW9" s="401"/>
+      <c r="BX9" s="401"/>
+      <c r="BY9" s="402"/>
+      <c r="BZ9" s="305"/>
+      <c r="CA9" s="305"/>
+      <c r="CB9" s="305"/>
       <c r="CC9" s="219" t="s">
         <v>3</v>
       </c>
@@ -15297,60 +15298,60 @@
       <c r="CG9" s="135"/>
     </row>
     <row r="10" spans="1:85" s="136" customFormat="1" ht="42">
-      <c r="A10" s="300"/>
-      <c r="B10" s="300"/>
-      <c r="C10" s="249"/>
-      <c r="D10" s="303"/>
-      <c r="E10" s="303"/>
-      <c r="F10" s="385"/>
-      <c r="G10" s="306"/>
-      <c r="H10" s="274"/>
-      <c r="I10" s="274"/>
-      <c r="J10" s="306"/>
-      <c r="K10" s="282"/>
-      <c r="L10" s="282"/>
-      <c r="M10" s="282"/>
-      <c r="N10" s="282"/>
-      <c r="O10" s="282"/>
-      <c r="P10" s="282"/>
-      <c r="Q10" s="282"/>
-      <c r="R10" s="282"/>
-      <c r="S10" s="282"/>
-      <c r="T10" s="282"/>
-      <c r="U10" s="282"/>
+      <c r="A10" s="281"/>
+      <c r="B10" s="281"/>
+      <c r="C10" s="263"/>
+      <c r="D10" s="273"/>
+      <c r="E10" s="273"/>
+      <c r="F10" s="411"/>
+      <c r="G10" s="260"/>
+      <c r="H10" s="290"/>
+      <c r="I10" s="290"/>
+      <c r="J10" s="260"/>
+      <c r="K10" s="247"/>
+      <c r="L10" s="247"/>
+      <c r="M10" s="247"/>
+      <c r="N10" s="247"/>
+      <c r="O10" s="247"/>
+      <c r="P10" s="247"/>
+      <c r="Q10" s="247"/>
+      <c r="R10" s="247"/>
+      <c r="S10" s="247"/>
+      <c r="T10" s="247"/>
+      <c r="U10" s="247"/>
       <c r="V10" s="222" t="s">
         <v>87</v>
       </c>
       <c r="W10" s="222" t="s">
         <v>88</v>
       </c>
-      <c r="X10" s="282"/>
-      <c r="Y10" s="285"/>
-      <c r="Z10" s="285"/>
-      <c r="AA10" s="285"/>
-      <c r="AB10" s="285"/>
-      <c r="AC10" s="285"/>
-      <c r="AD10" s="285"/>
-      <c r="AE10" s="285"/>
-      <c r="AF10" s="285"/>
-      <c r="AG10" s="285"/>
-      <c r="AH10" s="285"/>
-      <c r="AI10" s="285"/>
-      <c r="AJ10" s="292"/>
-      <c r="AK10" s="266"/>
-      <c r="AL10" s="314"/>
-      <c r="AM10" s="285"/>
-      <c r="AN10" s="249"/>
-      <c r="AO10" s="249"/>
-      <c r="AP10" s="306"/>
-      <c r="AQ10" s="306"/>
-      <c r="AR10" s="306"/>
-      <c r="AS10" s="306"/>
-      <c r="AT10" s="306"/>
-      <c r="AU10" s="306"/>
-      <c r="AV10" s="249"/>
-      <c r="AW10" s="314"/>
-      <c r="AX10" s="249"/>
+      <c r="X10" s="247"/>
+      <c r="Y10" s="257"/>
+      <c r="Z10" s="257"/>
+      <c r="AA10" s="257"/>
+      <c r="AB10" s="257"/>
+      <c r="AC10" s="257"/>
+      <c r="AD10" s="257"/>
+      <c r="AE10" s="257"/>
+      <c r="AF10" s="257"/>
+      <c r="AG10" s="257"/>
+      <c r="AH10" s="257"/>
+      <c r="AI10" s="257"/>
+      <c r="AJ10" s="302"/>
+      <c r="AK10" s="254"/>
+      <c r="AL10" s="269"/>
+      <c r="AM10" s="257"/>
+      <c r="AN10" s="263"/>
+      <c r="AO10" s="263"/>
+      <c r="AP10" s="260"/>
+      <c r="AQ10" s="260"/>
+      <c r="AR10" s="260"/>
+      <c r="AS10" s="260"/>
+      <c r="AT10" s="260"/>
+      <c r="AU10" s="260"/>
+      <c r="AV10" s="263"/>
+      <c r="AW10" s="269"/>
+      <c r="AX10" s="263"/>
       <c r="AY10" s="226" t="s">
         <v>89</v>
       </c>
@@ -15360,26 +15361,26 @@
       <c r="BA10" s="226" t="s">
         <v>91</v>
       </c>
-      <c r="BB10" s="408"/>
-      <c r="BC10" s="402"/>
-      <c r="BD10" s="402"/>
-      <c r="BE10" s="387"/>
-      <c r="BF10" s="387"/>
-      <c r="BG10" s="387"/>
-      <c r="BH10" s="402"/>
-      <c r="BI10" s="387"/>
-      <c r="BJ10" s="406"/>
-      <c r="BK10" s="402"/>
-      <c r="BL10" s="404"/>
-      <c r="BM10" s="402"/>
-      <c r="BN10" s="404"/>
-      <c r="BO10" s="404"/>
-      <c r="BP10" s="249"/>
-      <c r="BQ10" s="249"/>
-      <c r="BR10" s="249"/>
-      <c r="BS10" s="249"/>
-      <c r="BT10" s="249"/>
-      <c r="BU10" s="254"/>
+      <c r="BB10" s="391"/>
+      <c r="BC10" s="389"/>
+      <c r="BD10" s="389"/>
+      <c r="BE10" s="393"/>
+      <c r="BF10" s="393"/>
+      <c r="BG10" s="393"/>
+      <c r="BH10" s="389"/>
+      <c r="BI10" s="393"/>
+      <c r="BJ10" s="387"/>
+      <c r="BK10" s="389"/>
+      <c r="BL10" s="385"/>
+      <c r="BM10" s="389"/>
+      <c r="BN10" s="385"/>
+      <c r="BO10" s="385"/>
+      <c r="BP10" s="263"/>
+      <c r="BQ10" s="263"/>
+      <c r="BR10" s="263"/>
+      <c r="BS10" s="263"/>
+      <c r="BT10" s="263"/>
+      <c r="BU10" s="308"/>
       <c r="BV10" s="224" t="s">
         <v>92</v>
       </c>
@@ -15392,9 +15393,9 @@
       <c r="BY10" s="243" t="s">
         <v>95</v>
       </c>
-      <c r="BZ10" s="246"/>
-      <c r="CA10" s="246"/>
-      <c r="CB10" s="246"/>
+      <c r="BZ10" s="305"/>
+      <c r="CA10" s="305"/>
+      <c r="CB10" s="305"/>
       <c r="CC10" s="242">
         <v>25</v>
       </c>
@@ -15403,7 +15404,7 @@
       <c r="CG10" s="135"/>
     </row>
     <row r="11" spans="1:85" s="144" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A11" s="414">
+      <c r="A11" s="244">
         <v>1</v>
       </c>
       <c r="B11" s="228">
@@ -15416,7 +15417,7 @@
         <v>99</v>
       </c>
       <c r="E11" s="231" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F11" s="231" t="s">
         <v>101</v>
@@ -15430,7 +15431,7 @@
       </c>
       <c r="I11" s="232">
         <f t="shared" ref="I11:I17" si="1">BZ11-BX11-G11-H11</f>
-        <v>49700000</v>
+        <v>52700000</v>
       </c>
       <c r="J11" s="233">
         <v>1</v>
@@ -15525,7 +15526,7 @@
       </c>
       <c r="AO11" s="232">
         <f t="shared" ref="AO11:AO17" si="5">IF(F11="LN",I11*(K11+L11)/26+(H11+I11)*50%*M11/26+IF(F11="LT",BU11*O11/26-AB11,0)+MAX($G11*P11/26*150%,P11*$BU11/26)-AC11+MAX($G11*Q11/26*200%,Q11*$BU11/26)-AD11+MAX($G11*R11/26*300%,R11*$BU11/26)-AE11+BU11*S11/26-AF11+AH11-AG11,I11-I11*($CC$10-K11-L11)/26+(H11+I11)*50%*M11/26+IF(F11="LT",BU11*O11/26-AB11,0)+MAX($G11*P11/26*150%,P11*$BU11/26)-AC11+MAX($G11*Q11/26*200%,Q11*$BU11/26)-AD11+MAX($G11*R11/26*300%,R11*$BU11/26)-AE11+BU11*S11/26-AF11+AH11-AG11+(G11-G11*($CC$10-K11-L11)/26-Y11)+(H11-H11*($CC$10-K11-L11)/26-AN11))</f>
-        <v>27217692.307692312</v>
+        <v>28602307.692307696</v>
       </c>
       <c r="AP11" s="232"/>
       <c r="AQ11" s="232"/>
@@ -15535,11 +15536,12 @@
       <c r="AU11" s="232"/>
       <c r="AV11" s="232">
         <f>Y11+Z11+AA11+AB11+AC11+AD11+AE11+AF11+AG11+AI11+AJ11+AK11+AL11+AM11+AN11+AO11+AP11-AQ11+AR11+AS11+AT11+AU11</f>
-        <v>32307692.307692312</v>
+        <v>33692307.692307696</v>
       </c>
       <c r="AW11" s="232"/>
-      <c r="AX11" s="232" t="s">
-        <v>102</v>
+      <c r="AX11" s="232" t="str">
+        <f t="shared" ref="AX11:AX17" si="6">IF(E11="CT","x",0)</f>
+        <v>x</v>
       </c>
       <c r="AY11" s="235">
         <f>ROUND(IF($AX11="x",($G11+$H11)*AY$10,0),0)</f>
@@ -15564,23 +15566,23 @@
         <v>95200</v>
       </c>
       <c r="BF11" s="235">
-        <f>AM11+IF(AR11&gt;="730000",730000,AR11)+IF(((AV11-AM11-IF(AR11&gt;="730000",730000,AR11)-AS11)*15%-AS11)&gt;"0",((AV11-AM11-IF(AR11&gt;="730000",730000,AR11)-AS11)*15%-AS11),0)</f>
-        <v>0</v>
+        <f>AM11+IF(AR11&gt;=730000,730000,AR11)+IF(((AV11-AM11-IF(AR11&gt;=730000,730000,AR11)-AS11)*15%-AS11)&gt;0,((AV11-AM11-IF(AR11&gt;=730000,730000,AR11)-AS11)*15%-AS11),0)</f>
+        <v>5053846.153846154</v>
       </c>
       <c r="BG11" s="235">
         <f>AV11-BF11+AW11</f>
-        <v>32307692.307692312</v>
+        <v>28638461.538461544</v>
       </c>
       <c r="BH11" s="235">
         <v>3</v>
       </c>
       <c r="BI11" s="235">
         <f>BG11-BB11-BC11+BD11-BH11*4400000-IF(E11="CT",11000000,0)</f>
-        <v>18026192.307692312</v>
+        <v>3356961.5384615436</v>
       </c>
       <c r="BJ11" s="236">
         <f>IF(BI11&gt;0,ROUND(IF(BI11&gt;=80000000,BI11*35%-9850000,IF(BI11&gt;=52000000,BI11*30%-5850000,IF(BI11&gt;=32000000,BI11*25%-3250000,IF(BI11&gt;=18000000,BI11*20%-1650000,IF(BI11&gt;=10000000,BI11*15%-750000,IF(BI11&gt;5000000,BI11*10%-250000,BI11*5%)))))),0),0)</f>
-        <v>1955238</v>
+        <v>167848</v>
       </c>
       <c r="BK11" s="235"/>
       <c r="BL11" s="235"/>
@@ -15598,7 +15600,7 @@
       </c>
       <c r="BT11" s="235">
         <f>AV11*BS11-BN11-BK11-BP11-BO11</f>
-        <v>25846153.846153852</v>
+        <v>26953846.15384616</v>
       </c>
       <c r="BU11" s="239">
         <v>60000000</v>
@@ -15609,11 +15611,12 @@
       <c r="BW11" s="236"/>
       <c r="BX11" s="236"/>
       <c r="BY11" s="236">
-        <v>0</v>
+        <f t="shared" ref="BY11:BY17" si="7">+BU11*5%</f>
+        <v>3000000</v>
       </c>
       <c r="BZ11" s="236">
         <f>SUM(BU11:BY11)</f>
-        <v>60000000</v>
+        <v>63000000</v>
       </c>
       <c r="CA11" s="236" t="s">
         <v>123</v>
@@ -15691,39 +15694,39 @@
         <v>0</v>
       </c>
       <c r="Y12" s="14">
-        <f t="shared" ref="Y12:Y13" si="6">G12*(K12+L12)/26</f>
+        <f t="shared" ref="Y12:Y13" si="8">G12*(K12+L12)/26</f>
         <v>3424615.3846153845</v>
       </c>
       <c r="Z12" s="14">
-        <f t="shared" ref="Z12:Z13" si="7">M12*G12/26</f>
+        <f t="shared" ref="Z12:Z13" si="9">M12*G12/26</f>
         <v>163076.92307692306</v>
       </c>
       <c r="AA12" s="14">
-        <f t="shared" ref="AA12:AA13" si="8">G12*N12/26</f>
+        <f t="shared" ref="AA12:AA13" si="10">G12*N12/26</f>
         <v>0</v>
       </c>
       <c r="AB12" s="14">
-        <f t="shared" ref="AB12:AB13" si="9">G12*O12/26</f>
+        <f t="shared" ref="AB12:AB13" si="11">G12*O12/26</f>
         <v>652307.69230769225</v>
       </c>
       <c r="AC12" s="14">
-        <f t="shared" ref="AC12:AC13" si="10">G12*P12*150%/26</f>
+        <f t="shared" ref="AC12:AC13" si="12">G12*P12*150%/26</f>
         <v>0</v>
       </c>
       <c r="AD12" s="14">
-        <f t="shared" ref="AD12:AD13" si="11">G12*Q12/26*200%</f>
+        <f t="shared" ref="AD12:AD13" si="13">G12*Q12/26*200%</f>
         <v>0</v>
       </c>
       <c r="AE12" s="14">
-        <f t="shared" ref="AE12:AE13" si="12">G12*R12/26*300%</f>
+        <f t="shared" ref="AE12:AE13" si="14">G12*R12/26*300%</f>
         <v>0</v>
       </c>
       <c r="AF12" s="14">
-        <f t="shared" ref="AF12:AF13" si="13">IF(F12="LT",0,(G12+H12)/26*S12*30%)</f>
+        <f t="shared" ref="AF12:AF13" si="15">IF(F12="LT",0,(G12+H12)/26*S12*30%)</f>
         <v>0</v>
       </c>
       <c r="AG12" s="14">
-        <f t="shared" ref="AG12:AG13" si="14">T12*G12/23/8</f>
+        <f t="shared" ref="AG12:AG13" si="16">T12*G12/23/8</f>
         <v>0</v>
       </c>
       <c r="AH12" s="14">
@@ -15731,7 +15734,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="14">
-        <f t="shared" ref="AI12:AI13" si="15">G12*V12/26</f>
+        <f t="shared" ref="AI12:AI13" si="17">G12*V12/26</f>
         <v>0</v>
       </c>
       <c r="AJ12" s="14"/>
@@ -15745,7 +15748,7 @@
         <v>0</v>
       </c>
       <c r="AN12" s="14">
-        <f t="shared" ref="AN12:AN13" si="16">H12/26*K12</f>
+        <f t="shared" ref="AN12:AN13" si="18">H12/26*K12</f>
         <v>315000</v>
       </c>
       <c r="AO12" s="14">
@@ -15759,23 +15762,24 @@
       <c r="AT12" s="14"/>
       <c r="AU12" s="14"/>
       <c r="AV12" s="14">
-        <f t="shared" ref="AV12:AV13" si="17">Y12+Z12+AA12+AB12+AC12+AD12+AE12+AF12+AG12+AI12+AJ12+AK12+AL12+AM12+AN12+AO12+AP12-AQ12+AR12+AS12+AT12+AU12</f>
+        <f t="shared" ref="AV12:AV13" si="19">Y12+Z12+AA12+AB12+AC12+AD12+AE12+AF12+AG12+AI12+AJ12+AK12+AL12+AM12+AN12+AO12+AP12-AQ12+AR12+AS12+AT12+AU12</f>
         <v>22139230.769230772</v>
       </c>
       <c r="AW12" s="14"/>
-      <c r="AX12" s="14" t="s">
-        <v>102</v>
+      <c r="AX12" s="14" t="str">
+        <f t="shared" si="6"/>
+        <v>x</v>
       </c>
       <c r="AY12" s="13">
-        <f t="shared" ref="AY12:AY17" si="18">ROUND(IF($AX12="x",($G12+$H12)*AY$10,0),0)</f>
+        <f t="shared" ref="AY12:AY17" si="20">ROUND(IF($AX12="x",($G12+$H12)*AY$10,0),0)</f>
         <v>740800</v>
       </c>
       <c r="AZ12" s="13">
-        <f t="shared" ref="AZ12:BA17" si="19">ROUND(IF($AX12="x",($G12+$H12)*AZ$10,0),0)</f>
+        <f t="shared" ref="AZ12:BA17" si="21">ROUND(IF($AX12="x",($G12+$H12)*AZ$10,0),0)</f>
         <v>138900</v>
       </c>
       <c r="BA12" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>92600</v>
       </c>
       <c r="BB12" s="13">
@@ -15785,25 +15789,25 @@
       <c r="BC12" s="13"/>
       <c r="BD12" s="13"/>
       <c r="BE12" s="13">
-        <f t="shared" ref="BE12:BE13" si="20">IF(G12*1%&gt;=234000,234000,G12*1%)</f>
+        <f t="shared" ref="BE12:BE13" si="22">IF(G12*1%&gt;=234000,234000,G12*1%)</f>
         <v>84800</v>
       </c>
       <c r="BF12" s="13">
-        <f t="shared" ref="BF12:BF13" si="21">AM12+IF(AR12&gt;="730000",730000,AR12)+IF(((AV12-AM12-IF(AR12&gt;="730000",730000,AR12)-AS12)*15%-AS12)&gt;"0",((AV12-AM12-IF(AR12&gt;="730000",730000,AR12)-AS12)*15%-AS12),0)</f>
-        <v>0</v>
+        <f t="shared" ref="BF12:BF17" si="23">AM12+IF(AR12&gt;=730000,730000,AR12)+IF(((AV12-AM12-IF(AR12&gt;=730000,730000,AR12)-AS12)*15%-AS12)&gt;0,((AV12-AM12-IF(AR12&gt;=730000,730000,AR12)-AS12)*15%-AS12),0)</f>
+        <v>3320884.6153846155</v>
       </c>
       <c r="BG12" s="13">
-        <f t="shared" ref="BG12:BG13" si="22">AV12-BF12+AW12</f>
-        <v>22139230.769230772</v>
+        <f t="shared" ref="BG12:BG13" si="24">AV12-BF12+AW12</f>
+        <v>18818346.153846156</v>
       </c>
       <c r="BH12" s="13"/>
       <c r="BI12" s="13">
-        <f t="shared" ref="BI12:BI13" si="23">BG12-BB12-BC12+BD12-BH12*4400000-IF(E12="CT",11000000,0)</f>
-        <v>10166930.769230772</v>
+        <f t="shared" ref="BI12:BI13" si="25">BG12-BB12-BC12+BD12-BH12*4400000-IF(E12="CT",11000000,0)</f>
+        <v>6846046.1538461559</v>
       </c>
       <c r="BJ12" s="12">
-        <f t="shared" ref="BJ12:BJ13" si="24">IF(BI12&gt;0,ROUND(IF(BI12&gt;=80000000,BI12*35%-9850000,IF(BI12&gt;=52000000,BI12*30%-5850000,IF(BI12&gt;=32000000,BI12*25%-3250000,IF(BI12&gt;=18000000,BI12*20%-1650000,IF(BI12&gt;=10000000,BI12*15%-750000,IF(BI12&gt;5000000,BI12*10%-250000,BI12*5%)))))),0),0)</f>
-        <v>775040</v>
+        <f t="shared" ref="BJ12:BJ13" si="26">IF(BI12&gt;0,ROUND(IF(BI12&gt;=80000000,BI12*35%-9850000,IF(BI12&gt;=52000000,BI12*30%-5850000,IF(BI12&gt;=32000000,BI12*25%-3250000,IF(BI12&gt;=18000000,BI12*20%-1650000,IF(BI12&gt;=10000000,BI12*15%-750000,IF(BI12&gt;5000000,BI12*10%-250000,BI12*5%)))))),0),0)</f>
+        <v>434605</v>
       </c>
       <c r="BK12" s="13"/>
       <c r="BL12" s="13"/>
@@ -15816,11 +15820,11 @@
       <c r="BQ12" s="13"/>
       <c r="BR12" s="13"/>
       <c r="BS12" s="13" t="str">
-        <f t="shared" ref="BS12:BS13" si="25">IF(AV12&gt;=11000000,"80%","100%")</f>
+        <f t="shared" ref="BS12:BS13" si="27">IF(AV12&gt;=11000000,"80%","100%")</f>
         <v>80%</v>
       </c>
       <c r="BT12" s="13">
-        <f t="shared" ref="BT12:BT13" si="26">AV12*BS12-BN12-BK12-BP12-BO12</f>
+        <f t="shared" ref="BT12:BT13" si="28">AV12*BS12-BN12-BK12-BP12-BO12</f>
         <v>17711384.61538462</v>
       </c>
       <c r="BU12" s="22">
@@ -15834,11 +15838,11 @@
       </c>
       <c r="BX12" s="12"/>
       <c r="BY12" s="12">
-        <f t="shared" ref="BY12:BY17" si="27">+BU12*5%</f>
+        <f t="shared" si="7"/>
         <v>2000000</v>
       </c>
       <c r="BZ12" s="12">
-        <f t="shared" ref="BZ12:BZ13" si="28">SUM(BU12:BY12)</f>
+        <f t="shared" ref="BZ12:BZ13" si="29">SUM(BU12:BY12)</f>
         <v>42000000</v>
       </c>
       <c r="CA12" s="12" t="s">
@@ -15915,39 +15919,39 @@
         <v>0</v>
       </c>
       <c r="Y13" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>3308461.5384615385</v>
       </c>
       <c r="Z13" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA13" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AB13" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>601538.4615384615</v>
       </c>
       <c r="AC13" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AD13" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AE13" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>3609230.769230769</v>
       </c>
       <c r="AF13" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AG13" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AH13" s="14">
@@ -15955,7 +15959,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ13" s="14"/>
@@ -15969,7 +15973,7 @@
         <v>0</v>
       </c>
       <c r="AN13" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>126923.07692307694</v>
       </c>
       <c r="AO13" s="14">
@@ -15983,51 +15987,52 @@
       <c r="AT13" s="14"/>
       <c r="AU13" s="14"/>
       <c r="AV13" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>28615384.615384616</v>
       </c>
       <c r="AW13" s="14"/>
-      <c r="AX13" s="14" t="s">
-        <v>102</v>
+      <c r="AX13" s="14" t="str">
+        <f t="shared" si="6"/>
+        <v>x</v>
       </c>
       <c r="AY13" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>649600</v>
       </c>
       <c r="AZ13" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>121800</v>
       </c>
       <c r="BA13" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>81200</v>
       </c>
       <c r="BB13" s="13">
-        <f t="shared" ref="BB13" si="29">SUM(AY13:BA13)</f>
+        <f t="shared" ref="BB13" si="30">SUM(AY13:BA13)</f>
         <v>852600</v>
       </c>
       <c r="BC13" s="13"/>
       <c r="BD13" s="13"/>
       <c r="BE13" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>78200</v>
       </c>
       <c r="BF13" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>4292307.692307692</v>
       </c>
       <c r="BG13" s="13">
-        <f t="shared" si="22"/>
-        <v>28615384.615384616</v>
+        <f t="shared" si="24"/>
+        <v>24323076.923076924</v>
       </c>
       <c r="BH13" s="13"/>
       <c r="BI13" s="13">
-        <f t="shared" si="23"/>
-        <v>16762784.615384616</v>
+        <f t="shared" si="25"/>
+        <v>12470476.923076924</v>
       </c>
       <c r="BJ13" s="12">
-        <f t="shared" si="24"/>
-        <v>1764418</v>
+        <f t="shared" si="26"/>
+        <v>1120572</v>
       </c>
       <c r="BK13" s="13"/>
       <c r="BL13" s="13"/>
@@ -16040,11 +16045,11 @@
       <c r="BQ13" s="13"/>
       <c r="BR13" s="13"/>
       <c r="BS13" s="13" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>80%</v>
       </c>
       <c r="BT13" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>22892307.692307696</v>
       </c>
       <c r="BU13" s="22">
@@ -16058,11 +16063,11 @@
       </c>
       <c r="BX13" s="12"/>
       <c r="BY13" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="7"/>
         <v>2000000</v>
       </c>
       <c r="BZ13" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>42000000</v>
       </c>
       <c r="CA13" s="12" t="s">
@@ -16141,39 +16146,39 @@
         <v>0</v>
       </c>
       <c r="Y14" s="14">
-        <f t="shared" ref="Y14:Y15" si="30">G14*(K14+L14)/26</f>
+        <f t="shared" ref="Y14:Y15" si="31">G14*(K14+L14)/26</f>
         <v>2822884.6153846155</v>
       </c>
       <c r="Z14" s="14">
-        <f t="shared" ref="Z14:Z15" si="31">M14*G14/26</f>
+        <f t="shared" ref="Z14:Z15" si="32">M14*G14/26</f>
         <v>134423.07692307694</v>
       </c>
       <c r="AA14" s="14">
-        <f t="shared" ref="AA14:AA15" si="32">G14*N14/26</f>
+        <f t="shared" ref="AA14:AA15" si="33">G14*N14/26</f>
         <v>0</v>
       </c>
       <c r="AB14" s="14">
-        <f t="shared" ref="AB14:AB15" si="33">G14*O14/26</f>
+        <f t="shared" ref="AB14:AB15" si="34">G14*O14/26</f>
         <v>537692.30769230775</v>
       </c>
       <c r="AC14" s="14">
-        <f t="shared" ref="AC14:AC15" si="34">G14*P14*150%/26</f>
+        <f t="shared" ref="AC14:AC15" si="35">G14*P14*150%/26</f>
         <v>0</v>
       </c>
       <c r="AD14" s="14">
-        <f t="shared" ref="AD14:AD15" si="35">G14*Q14/26*200%</f>
+        <f t="shared" ref="AD14:AD15" si="36">G14*Q14/26*200%</f>
         <v>0</v>
       </c>
       <c r="AE14" s="14">
-        <f t="shared" ref="AE14:AE15" si="36">G14*R14/26*300%</f>
+        <f t="shared" ref="AE14:AE15" si="37">G14*R14/26*300%</f>
         <v>0</v>
       </c>
       <c r="AF14" s="14">
-        <f t="shared" ref="AF14:AF15" si="37">IF(F14="LT",0,(G14+H14)/26*S14*30%)</f>
+        <f t="shared" ref="AF14:AF15" si="38">IF(F14="LT",0,(G14+H14)/26*S14*30%)</f>
         <v>0</v>
       </c>
       <c r="AG14" s="14">
-        <f t="shared" ref="AG14:AG15" si="38">T14*G14/23/8</f>
+        <f t="shared" ref="AG14:AG15" si="39">T14*G14/23/8</f>
         <v>0</v>
       </c>
       <c r="AH14" s="14">
@@ -16181,7 +16186,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="14">
-        <f t="shared" ref="AI14:AI15" si="39">G14*V14/26</f>
+        <f t="shared" ref="AI14:AI15" si="40">G14*V14/26</f>
         <v>0</v>
       </c>
       <c r="AJ14" s="14"/>
@@ -16195,7 +16200,7 @@
         <v>0</v>
       </c>
       <c r="AN14" s="14">
-        <f t="shared" ref="AN14:AN15" si="40">H14/26*K14</f>
+        <f t="shared" ref="AN14:AN15" si="41">H14/26*K14</f>
         <v>315000</v>
       </c>
       <c r="AO14" s="14">
@@ -16209,23 +16214,24 @@
       <c r="AT14" s="14"/>
       <c r="AU14" s="14"/>
       <c r="AV14" s="14">
-        <f t="shared" ref="AV14:AV15" si="41">Y14+Z14+AA14+AB14+AC14+AD14+AE14+AF14+AG14+AI14+AJ14+AK14+AL14+AM14+AN14+AO14+AP14-AQ14+AR14+AS14+AT14+AU14</f>
+        <f t="shared" ref="AV14:AV15" si="42">Y14+Z14+AA14+AB14+AC14+AD14+AE14+AF14+AG14+AI14+AJ14+AK14+AL14+AM14+AN14+AO14+AP14-AQ14+AR14+AS14+AT14+AU14</f>
         <v>12750384.615384616</v>
       </c>
       <c r="AW14" s="14"/>
-      <c r="AX14" s="14" t="s">
-        <v>102</v>
+      <c r="AX14" s="14" t="str">
+        <f t="shared" si="6"/>
+        <v>x</v>
       </c>
       <c r="AY14" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>621600</v>
       </c>
       <c r="AZ14" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>116550</v>
       </c>
       <c r="BA14" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>77700</v>
       </c>
       <c r="BB14" s="13">
@@ -16235,25 +16241,25 @@
       <c r="BC14" s="13"/>
       <c r="BD14" s="13"/>
       <c r="BE14" s="13">
-        <f t="shared" ref="BE14:BE15" si="42">IF(G14*1%&gt;=234000,234000,G14*1%)</f>
+        <f t="shared" ref="BE14:BE15" si="43">IF(G14*1%&gt;=234000,234000,G14*1%)</f>
         <v>69900</v>
       </c>
       <c r="BF14" s="13">
-        <f t="shared" ref="BF14:BF15" si="43">AM14+IF(AR14&gt;="730000",730000,AR14)+IF(((AV14-AM14-IF(AR14&gt;="730000",730000,AR14)-AS14)*15%-AS14)&gt;"0",((AV14-AM14-IF(AR14&gt;="730000",730000,AR14)-AS14)*15%-AS14),0)</f>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>1912557.6923076923</v>
       </c>
       <c r="BG14" s="13">
         <f t="shared" ref="BG14:BG15" si="44">AV14-BF14+AW14</f>
-        <v>12750384.615384616</v>
+        <v>10837826.923076924</v>
       </c>
       <c r="BH14" s="13"/>
       <c r="BI14" s="13">
         <f t="shared" ref="BI14:BI15" si="45">BG14-BB14-BC14+BD14-BH14*4400000-IF(E14="CT",11000000,0)</f>
-        <v>934534.61538461596</v>
+        <v>-978023.07692307606</v>
       </c>
       <c r="BJ14" s="12">
         <f t="shared" ref="BJ14:BJ15" si="46">IF(BI14&gt;0,ROUND(IF(BI14&gt;=80000000,BI14*35%-9850000,IF(BI14&gt;=52000000,BI14*30%-5850000,IF(BI14&gt;=32000000,BI14*25%-3250000,IF(BI14&gt;=18000000,BI14*20%-1650000,IF(BI14&gt;=10000000,BI14*15%-750000,IF(BI14&gt;5000000,BI14*10%-250000,BI14*5%)))))),0),0)</f>
-        <v>46727</v>
+        <v>0</v>
       </c>
       <c r="BK14" s="13"/>
       <c r="BL14" s="13"/>
@@ -16284,7 +16290,7 @@
       </c>
       <c r="BX14" s="12"/>
       <c r="BY14" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="7"/>
         <v>1150000</v>
       </c>
       <c r="BZ14" s="12">
@@ -16365,39 +16371,39 @@
         <v>0</v>
       </c>
       <c r="Y15" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2051923.076923077</v>
       </c>
       <c r="Z15" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AA15" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AB15" s="14">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>373076.92307692306</v>
       </c>
       <c r="AC15" s="14">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD15" s="14">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AE15" s="14">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2238461.5384615385</v>
       </c>
       <c r="AF15" s="14">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AG15" s="14">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AH15" s="14">
@@ -16405,7 +16411,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="14">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AJ15" s="14"/>
@@ -16419,7 +16425,7 @@
         <v>0</v>
       </c>
       <c r="AN15" s="14">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>126923.07692307694</v>
       </c>
       <c r="AO15" s="14">
@@ -16433,23 +16439,24 @@
       <c r="AT15" s="14"/>
       <c r="AU15" s="14"/>
       <c r="AV15" s="14">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>7498076.9230769221</v>
       </c>
       <c r="AW15" s="14"/>
-      <c r="AX15" s="14" t="s">
-        <v>102</v>
+      <c r="AX15" s="14" t="str">
+        <f t="shared" si="6"/>
+        <v>x</v>
       </c>
       <c r="AY15" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>412000</v>
       </c>
       <c r="AZ15" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>77250</v>
       </c>
       <c r="BA15" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>51500</v>
       </c>
       <c r="BB15" s="13">
@@ -16459,21 +16466,21 @@
       <c r="BC15" s="13"/>
       <c r="BD15" s="13"/>
       <c r="BE15" s="13">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>48500</v>
       </c>
       <c r="BF15" s="13">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>1124711.5384615383</v>
       </c>
       <c r="BG15" s="13">
         <f t="shared" si="44"/>
-        <v>7498076.9230769221</v>
+        <v>6373365.384615384</v>
       </c>
       <c r="BH15" s="13"/>
       <c r="BI15" s="13">
         <f t="shared" si="45"/>
-        <v>-4042673.0769230779</v>
+        <v>-5167384.615384616</v>
       </c>
       <c r="BJ15" s="12">
         <f t="shared" si="46"/>
@@ -16508,7 +16515,7 @@
       </c>
       <c r="BX15" s="12"/>
       <c r="BY15" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="7"/>
         <v>550000</v>
       </c>
       <c r="BZ15" s="12">
@@ -16539,7 +16546,7 @@
         <v>104</v>
       </c>
       <c r="E16" s="141" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="F16" s="141" t="s">
         <v>101</v>
@@ -16663,24 +16670,25 @@
         <v>12744134.615384616</v>
       </c>
       <c r="AW16" s="14"/>
-      <c r="AX16" s="14" t="s">
-        <v>102</v>
+      <c r="AX16" s="14">
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AY16" s="13">
-        <f t="shared" si="18"/>
-        <v>569600</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AZ16" s="13">
-        <f t="shared" si="19"/>
-        <v>106800</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="BA16" s="13">
-        <f t="shared" si="19"/>
-        <v>71200</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="BB16" s="13">
         <f>SUM(AY16:BA16)</f>
-        <v>747600</v>
+        <v>0</v>
       </c>
       <c r="BC16" s="13"/>
       <c r="BD16" s="13"/>
@@ -16689,21 +16697,21 @@
         <v>63400</v>
       </c>
       <c r="BF16" s="13">
-        <f t="shared" ref="BF16:BF17" si="64">AM16+IF(AR16&gt;="730000",730000,AR16)+IF(((AV16-AM16-IF(AR16&gt;="730000",730000,AR16)-AS16)*15%-AS16)&gt;"0",((AV16-AM16-IF(AR16&gt;="730000",730000,AR16)-AS16)*15%-AS16),0)</f>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>1911620.1923076923</v>
       </c>
       <c r="BG16" s="13">
-        <f t="shared" ref="BG16:BG17" si="65">AV16-BF16+AW16</f>
-        <v>12744134.615384616</v>
+        <f t="shared" ref="BG16:BG17" si="64">AV16-BF16+AW16</f>
+        <v>10832514.423076924</v>
       </c>
       <c r="BH16" s="13"/>
       <c r="BI16" s="13">
-        <f t="shared" ref="BI16:BI17" si="66">BG16-BB16-BC16+BD16-BH16*4400000-IF(E16="CT",11000000,0)</f>
-        <v>996534.61538461596</v>
+        <f t="shared" ref="BI16:BI17" si="65">BG16-BB16-BC16+BD16-BH16*4400000-IF(E16="CT",11000000,0)</f>
+        <v>10832514.423076924</v>
       </c>
       <c r="BJ16" s="12">
-        <f t="shared" ref="BJ16:BJ17" si="67">IF(BI16&gt;0,ROUND(IF(BI16&gt;=80000000,BI16*35%-9850000,IF(BI16&gt;=52000000,BI16*30%-5850000,IF(BI16&gt;=32000000,BI16*25%-3250000,IF(BI16&gt;=18000000,BI16*20%-1650000,IF(BI16&gt;=10000000,BI16*15%-750000,IF(BI16&gt;5000000,BI16*10%-250000,BI16*5%)))))),0),0)</f>
-        <v>49827</v>
+        <f t="shared" ref="BJ16:BJ17" si="66">IF(BI16&gt;0,ROUND(IF(BI16&gt;=80000000,BI16*35%-9850000,IF(BI16&gt;=52000000,BI16*30%-5850000,IF(BI16&gt;=32000000,BI16*25%-3250000,IF(BI16&gt;=18000000,BI16*20%-1650000,IF(BI16&gt;=10000000,BI16*15%-750000,IF(BI16&gt;5000000,BI16*10%-250000,BI16*5%)))))),0),0)</f>
+        <v>874877</v>
       </c>
       <c r="BK16" s="13"/>
       <c r="BL16" s="13"/>
@@ -16716,11 +16724,11 @@
       <c r="BQ16" s="13"/>
       <c r="BR16" s="13"/>
       <c r="BS16" s="13" t="str">
-        <f t="shared" ref="BS16:BS17" si="68">IF(AV16&gt;=11000000,"80%","100%")</f>
+        <f t="shared" ref="BS16:BS17" si="67">IF(AV16&gt;=11000000,"80%","100%")</f>
         <v>80%</v>
       </c>
       <c r="BT16" s="13">
-        <f t="shared" ref="BT16:BT17" si="69">AV16*BS16-BN16-BK16-BP16-BO16</f>
+        <f t="shared" ref="BT16:BT17" si="68">AV16*BS16-BN16-BK16-BP16-BO16</f>
         <v>10195307.692307694</v>
       </c>
       <c r="BU16" s="22">
@@ -16734,11 +16742,11 @@
       </c>
       <c r="BX16" s="12"/>
       <c r="BY16" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="7"/>
         <v>1150000</v>
       </c>
       <c r="BZ16" s="12">
-        <f t="shared" ref="BZ16:BZ17" si="70">SUM(BU16:BY16)</f>
+        <f t="shared" ref="BZ16:BZ17" si="69">SUM(BU16:BY16)</f>
         <v>24150000</v>
       </c>
       <c r="CA16" s="12" t="s">
@@ -16887,23 +16895,24 @@
         <v>12472307.692307692</v>
       </c>
       <c r="AW17" s="14"/>
-      <c r="AX17" s="14" t="s">
-        <v>102</v>
+      <c r="AX17" s="14" t="str">
+        <f t="shared" si="6"/>
+        <v>x</v>
       </c>
       <c r="AY17" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>531200</v>
       </c>
       <c r="AZ17" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>99600</v>
       </c>
       <c r="BA17" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>66400</v>
       </c>
       <c r="BB17" s="13">
-        <f t="shared" ref="BB17" si="71">SUM(AY17:BA17)</f>
+        <f t="shared" ref="BB17" si="70">SUM(AY17:BA17)</f>
         <v>697200</v>
       </c>
       <c r="BC17" s="13"/>
@@ -16913,21 +16922,21 @@
         <v>63400</v>
       </c>
       <c r="BF17" s="13">
+        <f t="shared" si="23"/>
+        <v>1870846.1538461538</v>
+      </c>
+      <c r="BG17" s="13">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="BG17" s="13">
-        <f t="shared" si="65"/>
-        <v>12472307.692307692</v>
+        <v>10601461.538461538</v>
       </c>
       <c r="BH17" s="13"/>
       <c r="BI17" s="13">
+        <f t="shared" si="65"/>
+        <v>-1095738.461538462</v>
+      </c>
+      <c r="BJ17" s="12">
         <f t="shared" si="66"/>
-        <v>775107.69230769202</v>
-      </c>
-      <c r="BJ17" s="12">
-        <f t="shared" si="67"/>
-        <v>38755</v>
+        <v>0</v>
       </c>
       <c r="BK17" s="13"/>
       <c r="BL17" s="13"/>
@@ -16940,11 +16949,11 @@
       <c r="BQ17" s="13"/>
       <c r="BR17" s="13"/>
       <c r="BS17" s="13" t="str">
+        <f t="shared" si="67"/>
+        <v>80%</v>
+      </c>
+      <c r="BT17" s="13">
         <f t="shared" si="68"/>
-        <v>80%</v>
-      </c>
-      <c r="BT17" s="13">
-        <f t="shared" si="69"/>
         <v>9977846.153846154</v>
       </c>
       <c r="BU17" s="22">
@@ -16958,11 +16967,11 @@
       </c>
       <c r="BX17" s="12"/>
       <c r="BY17" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="7"/>
         <v>850000</v>
       </c>
       <c r="BZ17" s="12">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>17850000</v>
       </c>
       <c r="CA17" s="12" t="s">
@@ -17116,6 +17125,70 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="80">
+    <mergeCell ref="BU3:BZ5"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="D7:D10"/>
+    <mergeCell ref="E7:E10"/>
+    <mergeCell ref="F7:F10"/>
+    <mergeCell ref="G7:G10"/>
+    <mergeCell ref="H7:H10"/>
+    <mergeCell ref="I7:I10"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="K7:X7"/>
+    <mergeCell ref="Y7:AO7"/>
+    <mergeCell ref="AP7:AP10"/>
+    <mergeCell ref="Q8:Q10"/>
+    <mergeCell ref="BG9:BG10"/>
+    <mergeCell ref="AG8:AG10"/>
+    <mergeCell ref="U8:U10"/>
+    <mergeCell ref="V8:W9"/>
+    <mergeCell ref="X8:X10"/>
+    <mergeCell ref="Y8:Y10"/>
+    <mergeCell ref="Z8:Z10"/>
+    <mergeCell ref="P8:P10"/>
+    <mergeCell ref="AX7:AX10"/>
+    <mergeCell ref="AY7:BP7"/>
+    <mergeCell ref="BQ7:BR7"/>
+    <mergeCell ref="BT7:BT10"/>
+    <mergeCell ref="AF8:AF10"/>
+    <mergeCell ref="AV7:AV10"/>
+    <mergeCell ref="AW7:AW10"/>
+    <mergeCell ref="R8:R10"/>
+    <mergeCell ref="S8:S10"/>
+    <mergeCell ref="T8:T10"/>
+    <mergeCell ref="AA8:AA10"/>
+    <mergeCell ref="AB8:AB10"/>
+    <mergeCell ref="AC8:AC10"/>
+    <mergeCell ref="AD8:AD10"/>
+    <mergeCell ref="AE8:AE10"/>
+    <mergeCell ref="K8:K10"/>
+    <mergeCell ref="L8:L10"/>
+    <mergeCell ref="M8:M10"/>
+    <mergeCell ref="N8:N10"/>
+    <mergeCell ref="O8:O10"/>
+    <mergeCell ref="AU7:AU10"/>
+    <mergeCell ref="BV7:BY9"/>
+    <mergeCell ref="BZ7:BZ10"/>
+    <mergeCell ref="CA7:CA10"/>
+    <mergeCell ref="CB7:CB10"/>
+    <mergeCell ref="BU7:BU10"/>
+    <mergeCell ref="BF9:BF10"/>
+    <mergeCell ref="BC9:BC10"/>
+    <mergeCell ref="BD9:BD10"/>
+    <mergeCell ref="BE9:BE10"/>
+    <mergeCell ref="AH8:AH10"/>
+    <mergeCell ref="AI8:AI10"/>
+    <mergeCell ref="AJ8:AJ10"/>
+    <mergeCell ref="AK8:AK10"/>
+    <mergeCell ref="AL8:AL10"/>
+    <mergeCell ref="AM8:AM10"/>
+    <mergeCell ref="AQ7:AQ10"/>
+    <mergeCell ref="AN8:AN10"/>
+    <mergeCell ref="AO8:AO10"/>
+    <mergeCell ref="AR7:AR10"/>
+    <mergeCell ref="AS7:AS10"/>
+    <mergeCell ref="AT7:AT10"/>
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="BS7:BS10"/>
     <mergeCell ref="BO9:BO10"/>
@@ -17132,84 +17205,20 @@
     <mergeCell ref="BB9:BB10"/>
     <mergeCell ref="BH9:BH10"/>
     <mergeCell ref="BI9:BI10"/>
-    <mergeCell ref="BF9:BF10"/>
-    <mergeCell ref="BC9:BC10"/>
-    <mergeCell ref="BD9:BD10"/>
-    <mergeCell ref="BE9:BE10"/>
-    <mergeCell ref="AH8:AH10"/>
-    <mergeCell ref="AI8:AI10"/>
-    <mergeCell ref="AJ8:AJ10"/>
-    <mergeCell ref="AK8:AK10"/>
-    <mergeCell ref="AL8:AL10"/>
-    <mergeCell ref="AM8:AM10"/>
-    <mergeCell ref="AQ7:AQ10"/>
-    <mergeCell ref="AN8:AN10"/>
-    <mergeCell ref="AO8:AO10"/>
-    <mergeCell ref="AR7:AR10"/>
-    <mergeCell ref="AS7:AS10"/>
-    <mergeCell ref="AT7:AT10"/>
-    <mergeCell ref="AU7:AU10"/>
-    <mergeCell ref="BV7:BY9"/>
-    <mergeCell ref="BZ7:BZ10"/>
-    <mergeCell ref="CA7:CA10"/>
-    <mergeCell ref="CB7:CB10"/>
-    <mergeCell ref="K8:K10"/>
-    <mergeCell ref="L8:L10"/>
-    <mergeCell ref="M8:M10"/>
-    <mergeCell ref="N8:N10"/>
-    <mergeCell ref="O8:O10"/>
-    <mergeCell ref="P8:P10"/>
-    <mergeCell ref="AX7:AX10"/>
-    <mergeCell ref="AY7:BP7"/>
-    <mergeCell ref="BQ7:BR7"/>
-    <mergeCell ref="BT7:BT10"/>
-    <mergeCell ref="BU7:BU10"/>
-    <mergeCell ref="AF8:AF10"/>
-    <mergeCell ref="AV7:AV10"/>
-    <mergeCell ref="AW7:AW10"/>
-    <mergeCell ref="R8:R10"/>
-    <mergeCell ref="S8:S10"/>
-    <mergeCell ref="T8:T10"/>
-    <mergeCell ref="AA8:AA10"/>
-    <mergeCell ref="AB8:AB10"/>
-    <mergeCell ref="AC8:AC10"/>
-    <mergeCell ref="AD8:AD10"/>
-    <mergeCell ref="AE8:AE10"/>
-    <mergeCell ref="U8:U10"/>
-    <mergeCell ref="V8:W9"/>
-    <mergeCell ref="X8:X10"/>
-    <mergeCell ref="Y8:Y10"/>
-    <mergeCell ref="Z8:Z10"/>
-    <mergeCell ref="BU3:BZ5"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="D7:D10"/>
-    <mergeCell ref="E7:E10"/>
-    <mergeCell ref="F7:F10"/>
-    <mergeCell ref="G7:G10"/>
-    <mergeCell ref="H7:H10"/>
-    <mergeCell ref="I7:I10"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="K7:X7"/>
-    <mergeCell ref="Y7:AO7"/>
-    <mergeCell ref="AP7:AP10"/>
-    <mergeCell ref="Q8:Q10"/>
-    <mergeCell ref="BG9:BG10"/>
-    <mergeCell ref="AG8:AG10"/>
   </mergeCells>
+  <conditionalFormatting sqref="A7:A10">
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B11:B17">
-    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:B1048576 B1:B10">
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:B1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="82"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A10">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="82"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.21" bottom="0.17" header="0.196850393700787" footer="0.196850393700787"/>
@@ -17429,91 +17438,91 @@
       <c r="CD2" s="30"/>
     </row>
     <row r="3" spans="1:87" s="32" customFormat="1" outlineLevel="1">
-      <c r="A3" s="367" t="str">
+      <c r="A3" s="321" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
         <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
       </c>
-      <c r="B3" s="367"/>
-      <c r="C3" s="367"/>
-      <c r="D3" s="367"/>
-      <c r="E3" s="367"/>
-      <c r="F3" s="367"/>
-      <c r="G3" s="367"/>
-      <c r="H3" s="367"/>
-      <c r="I3" s="367"/>
-      <c r="J3" s="367"/>
-      <c r="K3" s="367"/>
-      <c r="L3" s="367"/>
-      <c r="M3" s="367"/>
-      <c r="N3" s="367"/>
-      <c r="O3" s="367"/>
-      <c r="P3" s="367"/>
-      <c r="Q3" s="367"/>
-      <c r="R3" s="367"/>
-      <c r="S3" s="367"/>
-      <c r="T3" s="367"/>
-      <c r="U3" s="367"/>
-      <c r="V3" s="367"/>
-      <c r="W3" s="367"/>
-      <c r="X3" s="367"/>
-      <c r="Y3" s="367"/>
-      <c r="Z3" s="367"/>
-      <c r="AA3" s="367"/>
-      <c r="AB3" s="367"/>
-      <c r="AC3" s="367"/>
-      <c r="AD3" s="367"/>
-      <c r="AE3" s="367"/>
-      <c r="AF3" s="367"/>
-      <c r="AG3" s="367"/>
-      <c r="AH3" s="367"/>
-      <c r="AI3" s="367"/>
-      <c r="AJ3" s="367"/>
-      <c r="AK3" s="367"/>
-      <c r="AL3" s="367"/>
-      <c r="AM3" s="367"/>
-      <c r="AN3" s="367"/>
-      <c r="AO3" s="367"/>
-      <c r="AP3" s="367"/>
-      <c r="AQ3" s="367"/>
-      <c r="AR3" s="367"/>
-      <c r="AS3" s="367"/>
-      <c r="AT3" s="367"/>
-      <c r="AU3" s="367"/>
-      <c r="AV3" s="367"/>
-      <c r="AW3" s="367"/>
-      <c r="AX3" s="367"/>
-      <c r="AY3" s="367"/>
-      <c r="AZ3" s="367"/>
-      <c r="BA3" s="367"/>
-      <c r="BB3" s="367"/>
-      <c r="BC3" s="367"/>
-      <c r="BD3" s="367"/>
-      <c r="BE3" s="367"/>
-      <c r="BF3" s="367"/>
-      <c r="BG3" s="367"/>
-      <c r="BH3" s="367"/>
-      <c r="BI3" s="367"/>
-      <c r="BJ3" s="367"/>
-      <c r="BK3" s="367"/>
-      <c r="BL3" s="367"/>
-      <c r="BM3" s="367"/>
-      <c r="BN3" s="367"/>
-      <c r="BO3" s="367"/>
-      <c r="BP3" s="367"/>
-      <c r="BQ3" s="367"/>
-      <c r="BR3" s="367"/>
-      <c r="BS3" s="367"/>
-      <c r="BT3" s="367"/>
-      <c r="BU3" s="367"/>
+      <c r="B3" s="321"/>
+      <c r="C3" s="321"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="321"/>
+      <c r="F3" s="321"/>
+      <c r="G3" s="321"/>
+      <c r="H3" s="321"/>
+      <c r="I3" s="321"/>
+      <c r="J3" s="321"/>
+      <c r="K3" s="321"/>
+      <c r="L3" s="321"/>
+      <c r="M3" s="321"/>
+      <c r="N3" s="321"/>
+      <c r="O3" s="321"/>
+      <c r="P3" s="321"/>
+      <c r="Q3" s="321"/>
+      <c r="R3" s="321"/>
+      <c r="S3" s="321"/>
+      <c r="T3" s="321"/>
+      <c r="U3" s="321"/>
+      <c r="V3" s="321"/>
+      <c r="W3" s="321"/>
+      <c r="X3" s="321"/>
+      <c r="Y3" s="321"/>
+      <c r="Z3" s="321"/>
+      <c r="AA3" s="321"/>
+      <c r="AB3" s="321"/>
+      <c r="AC3" s="321"/>
+      <c r="AD3" s="321"/>
+      <c r="AE3" s="321"/>
+      <c r="AF3" s="321"/>
+      <c r="AG3" s="321"/>
+      <c r="AH3" s="321"/>
+      <c r="AI3" s="321"/>
+      <c r="AJ3" s="321"/>
+      <c r="AK3" s="321"/>
+      <c r="AL3" s="321"/>
+      <c r="AM3" s="321"/>
+      <c r="AN3" s="321"/>
+      <c r="AO3" s="321"/>
+      <c r="AP3" s="321"/>
+      <c r="AQ3" s="321"/>
+      <c r="AR3" s="321"/>
+      <c r="AS3" s="321"/>
+      <c r="AT3" s="321"/>
+      <c r="AU3" s="321"/>
+      <c r="AV3" s="321"/>
+      <c r="AW3" s="321"/>
+      <c r="AX3" s="321"/>
+      <c r="AY3" s="321"/>
+      <c r="AZ3" s="321"/>
+      <c r="BA3" s="321"/>
+      <c r="BB3" s="321"/>
+      <c r="BC3" s="321"/>
+      <c r="BD3" s="321"/>
+      <c r="BE3" s="321"/>
+      <c r="BF3" s="321"/>
+      <c r="BG3" s="321"/>
+      <c r="BH3" s="321"/>
+      <c r="BI3" s="321"/>
+      <c r="BJ3" s="321"/>
+      <c r="BK3" s="321"/>
+      <c r="BL3" s="321"/>
+      <c r="BM3" s="321"/>
+      <c r="BN3" s="321"/>
+      <c r="BO3" s="321"/>
+      <c r="BP3" s="321"/>
+      <c r="BQ3" s="321"/>
+      <c r="BR3" s="321"/>
+      <c r="BS3" s="321"/>
+      <c r="BT3" s="321"/>
+      <c r="BU3" s="321"/>
       <c r="BV3"/>
-      <c r="BW3" s="368" t="s">
+      <c r="BW3" s="322" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="368"/>
-      <c r="BY3" s="368"/>
-      <c r="BZ3" s="368"/>
-      <c r="CA3" s="368"/>
-      <c r="CB3" s="367"/>
+      <c r="BX3" s="322"/>
+      <c r="BY3" s="322"/>
+      <c r="BZ3" s="322"/>
+      <c r="CA3" s="322"/>
+      <c r="CB3" s="321"/>
       <c r="CC3" s="31"/>
       <c r="CD3" s="31"/>
       <c r="CE3" s="32" t="s">
@@ -17597,368 +17606,368 @@
       <c r="BT4" s="33"/>
       <c r="BU4" s="33"/>
       <c r="BV4"/>
-      <c r="BW4" s="367"/>
-      <c r="BX4" s="367"/>
-      <c r="BY4" s="367"/>
-      <c r="BZ4" s="367"/>
-      <c r="CA4" s="367"/>
-      <c r="CB4" s="367"/>
+      <c r="BW4" s="321"/>
+      <c r="BX4" s="321"/>
+      <c r="BY4" s="321"/>
+      <c r="BZ4" s="321"/>
+      <c r="CA4" s="321"/>
+      <c r="CB4" s="321"/>
       <c r="CC4" s="31"/>
       <c r="CD4" s="31"/>
     </row>
     <row r="5" spans="1:87" s="34" customFormat="1">
-      <c r="A5" s="369" t="s">
+      <c r="A5" s="323" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="372" t="s">
+      <c r="B5" s="326" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="320" t="s">
+      <c r="C5" s="329" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="375" t="s">
+      <c r="D5" s="332" t="s">
         <v>142</v>
       </c>
-      <c r="E5" s="375" t="s">
+      <c r="E5" s="332" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="409" t="s">
+      <c r="F5" s="412" t="s">
         <v>143</v>
       </c>
-      <c r="G5" s="320" t="s">
+      <c r="G5" s="329" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="333" t="s">
+      <c r="H5" s="335" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="333" t="s">
+      <c r="I5" s="335" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="320" t="s">
+      <c r="J5" s="329" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="378" t="s">
+      <c r="K5" s="338" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="379"/>
-      <c r="M5" s="379"/>
-      <c r="N5" s="379"/>
-      <c r="O5" s="379"/>
-      <c r="P5" s="379"/>
-      <c r="Q5" s="379"/>
-      <c r="R5" s="379"/>
-      <c r="S5" s="379"/>
-      <c r="T5" s="379"/>
-      <c r="U5" s="379"/>
-      <c r="V5" s="379"/>
-      <c r="W5" s="379"/>
-      <c r="X5" s="379"/>
-      <c r="Y5" s="380" t="s">
+      <c r="L5" s="339"/>
+      <c r="M5" s="339"/>
+      <c r="N5" s="339"/>
+      <c r="O5" s="339"/>
+      <c r="P5" s="339"/>
+      <c r="Q5" s="339"/>
+      <c r="R5" s="339"/>
+      <c r="S5" s="339"/>
+      <c r="T5" s="339"/>
+      <c r="U5" s="339"/>
+      <c r="V5" s="339"/>
+      <c r="W5" s="339"/>
+      <c r="X5" s="339"/>
+      <c r="Y5" s="340" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="381"/>
-      <c r="AA5" s="381"/>
-      <c r="AB5" s="381"/>
-      <c r="AC5" s="381"/>
-      <c r="AD5" s="381"/>
-      <c r="AE5" s="381"/>
-      <c r="AF5" s="381"/>
-      <c r="AG5" s="381"/>
-      <c r="AH5" s="381"/>
-      <c r="AI5" s="381"/>
-      <c r="AJ5" s="381"/>
-      <c r="AK5" s="381"/>
-      <c r="AL5" s="381"/>
-      <c r="AM5" s="381"/>
-      <c r="AN5" s="381"/>
-      <c r="AO5" s="382"/>
-      <c r="AP5" s="320" t="s">
+      <c r="Z5" s="341"/>
+      <c r="AA5" s="341"/>
+      <c r="AB5" s="341"/>
+      <c r="AC5" s="341"/>
+      <c r="AD5" s="341"/>
+      <c r="AE5" s="341"/>
+      <c r="AF5" s="341"/>
+      <c r="AG5" s="341"/>
+      <c r="AH5" s="341"/>
+      <c r="AI5" s="341"/>
+      <c r="AJ5" s="341"/>
+      <c r="AK5" s="341"/>
+      <c r="AL5" s="341"/>
+      <c r="AM5" s="341"/>
+      <c r="AN5" s="341"/>
+      <c r="AO5" s="342"/>
+      <c r="AP5" s="329" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="320" t="s">
+      <c r="AQ5" s="329" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="320" t="s">
+      <c r="AR5" s="329" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="320" t="s">
+      <c r="AS5" s="329" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="320" t="s">
+      <c r="AT5" s="329" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="320" t="s">
+      <c r="AU5" s="329" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="320" t="s">
+      <c r="AV5" s="329" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="320" t="s">
+      <c r="AW5" s="329" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="320" t="s">
+      <c r="AX5" s="329" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="323" t="s">
+      <c r="AY5" s="350" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="324"/>
-      <c r="BA5" s="324"/>
-      <c r="BB5" s="324"/>
-      <c r="BC5" s="324"/>
-      <c r="BD5" s="324"/>
-      <c r="BE5" s="324"/>
-      <c r="BF5" s="324"/>
-      <c r="BG5" s="324"/>
-      <c r="BH5" s="324"/>
-      <c r="BI5" s="324"/>
-      <c r="BJ5" s="324"/>
-      <c r="BK5" s="324"/>
-      <c r="BL5" s="324"/>
-      <c r="BM5" s="324"/>
-      <c r="BN5" s="324"/>
-      <c r="BO5" s="324"/>
-      <c r="BP5" s="325"/>
-      <c r="BQ5" s="351" t="s">
+      <c r="AZ5" s="351"/>
+      <c r="BA5" s="351"/>
+      <c r="BB5" s="351"/>
+      <c r="BC5" s="351"/>
+      <c r="BD5" s="351"/>
+      <c r="BE5" s="351"/>
+      <c r="BF5" s="351"/>
+      <c r="BG5" s="351"/>
+      <c r="BH5" s="351"/>
+      <c r="BI5" s="351"/>
+      <c r="BJ5" s="351"/>
+      <c r="BK5" s="351"/>
+      <c r="BL5" s="351"/>
+      <c r="BM5" s="351"/>
+      <c r="BN5" s="351"/>
+      <c r="BO5" s="351"/>
+      <c r="BP5" s="352"/>
+      <c r="BQ5" s="353" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="360"/>
-      <c r="BS5" s="328" t="s">
+      <c r="BR5" s="354"/>
+      <c r="BS5" s="355" t="s">
         <v>144</v>
       </c>
-      <c r="BT5" s="328" t="s">
+      <c r="BT5" s="355" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="351" t="s">
+      <c r="BU5" s="353" t="s">
         <v>28</v>
       </c>
       <c r="BV5"/>
-      <c r="BW5" s="354" t="s">
+      <c r="BW5" s="376" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="339" t="s">
+      <c r="BX5" s="362" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="340"/>
-      <c r="BZ5" s="340"/>
-      <c r="CA5" s="341"/>
-      <c r="CB5" s="348" t="s">
+      <c r="BY5" s="363"/>
+      <c r="BZ5" s="363"/>
+      <c r="CA5" s="364"/>
+      <c r="CB5" s="371" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="244" t="s">
+      <c r="CC5" s="303" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="244" t="s">
+      <c r="CD5" s="303" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="35"/>
       <c r="CI5" s="36"/>
     </row>
     <row r="6" spans="1:87" s="34" customFormat="1">
-      <c r="A6" s="370"/>
-      <c r="B6" s="373"/>
-      <c r="C6" s="321"/>
-      <c r="D6" s="376"/>
-      <c r="E6" s="376"/>
-      <c r="F6" s="410"/>
-      <c r="G6" s="321"/>
-      <c r="H6" s="334"/>
-      <c r="I6" s="334"/>
-      <c r="J6" s="321"/>
-      <c r="K6" s="357" t="s">
+      <c r="A6" s="324"/>
+      <c r="B6" s="327"/>
+      <c r="C6" s="330"/>
+      <c r="D6" s="333"/>
+      <c r="E6" s="333"/>
+      <c r="F6" s="413"/>
+      <c r="G6" s="330"/>
+      <c r="H6" s="336"/>
+      <c r="I6" s="336"/>
+      <c r="J6" s="330"/>
+      <c r="K6" s="343" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="357" t="s">
+      <c r="L6" s="343" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="357" t="s">
+      <c r="M6" s="343" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="357" t="s">
+      <c r="N6" s="343" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="357" t="s">
+      <c r="O6" s="343" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="357" t="s">
+      <c r="P6" s="343" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="357" t="s">
+      <c r="Q6" s="343" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="357" t="s">
+      <c r="R6" s="343" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="357" t="s">
+      <c r="S6" s="343" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="357" t="s">
+      <c r="T6" s="343" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="357" t="s">
+      <c r="U6" s="343" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="363" t="s">
+      <c r="V6" s="346" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="364"/>
-      <c r="X6" s="357" t="s">
+      <c r="W6" s="347"/>
+      <c r="X6" s="343" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="320" t="s">
+      <c r="Y6" s="329" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="320" t="s">
+      <c r="Z6" s="329" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="320" t="s">
+      <c r="AA6" s="329" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="320" t="s">
+      <c r="AB6" s="329" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="333" t="s">
+      <c r="AC6" s="335" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="333" t="s">
+      <c r="AD6" s="335" t="s">
         <v>145</v>
       </c>
-      <c r="AE6" s="333" t="s">
+      <c r="AE6" s="335" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="333" t="s">
+      <c r="AF6" s="335" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="320" t="s">
+      <c r="AG6" s="329" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="333" t="s">
+      <c r="AH6" s="335" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="333" t="s">
+      <c r="AI6" s="335" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="320" t="s">
+      <c r="AJ6" s="329" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="336" t="s">
+      <c r="AK6" s="379" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="320" t="s">
+      <c r="AL6" s="329" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="320" t="s">
+      <c r="AM6" s="329" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="247" t="s">
+      <c r="AN6" s="261" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="320" t="s">
+      <c r="AO6" s="329" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="321"/>
-      <c r="AQ6" s="321"/>
-      <c r="AR6" s="321"/>
-      <c r="AS6" s="321"/>
-      <c r="AT6" s="321"/>
-      <c r="AU6" s="321"/>
-      <c r="AV6" s="321"/>
-      <c r="AW6" s="321"/>
-      <c r="AX6" s="321"/>
-      <c r="AY6" s="323" t="s">
+      <c r="AP6" s="330"/>
+      <c r="AQ6" s="330"/>
+      <c r="AR6" s="330"/>
+      <c r="AS6" s="330"/>
+      <c r="AT6" s="330"/>
+      <c r="AU6" s="330"/>
+      <c r="AV6" s="330"/>
+      <c r="AW6" s="330"/>
+      <c r="AX6" s="330"/>
+      <c r="AY6" s="350" t="s">
         <v>64</v>
       </c>
-      <c r="AZ6" s="324"/>
-      <c r="BA6" s="324"/>
-      <c r="BB6" s="324"/>
-      <c r="BC6" s="324"/>
-      <c r="BD6" s="324"/>
-      <c r="BE6" s="324"/>
-      <c r="BF6" s="324"/>
-      <c r="BG6" s="324"/>
-      <c r="BH6" s="324"/>
-      <c r="BI6" s="324"/>
-      <c r="BJ6" s="325"/>
-      <c r="BK6" s="323" t="s">
+      <c r="AZ6" s="351"/>
+      <c r="BA6" s="351"/>
+      <c r="BB6" s="351"/>
+      <c r="BC6" s="351"/>
+      <c r="BD6" s="351"/>
+      <c r="BE6" s="351"/>
+      <c r="BF6" s="351"/>
+      <c r="BG6" s="351"/>
+      <c r="BH6" s="351"/>
+      <c r="BI6" s="351"/>
+      <c r="BJ6" s="352"/>
+      <c r="BK6" s="350" t="s">
         <v>65</v>
       </c>
-      <c r="BL6" s="324"/>
-      <c r="BM6" s="324"/>
-      <c r="BN6" s="324"/>
-      <c r="BO6" s="324"/>
-      <c r="BP6" s="325"/>
-      <c r="BQ6" s="326" t="s">
+      <c r="BL6" s="351"/>
+      <c r="BM6" s="351"/>
+      <c r="BN6" s="351"/>
+      <c r="BO6" s="351"/>
+      <c r="BP6" s="352"/>
+      <c r="BQ6" s="356" t="s">
         <v>66</v>
       </c>
-      <c r="BR6" s="326" t="s">
+      <c r="BR6" s="356" t="s">
         <v>67</v>
       </c>
-      <c r="BS6" s="326"/>
-      <c r="BT6" s="326"/>
-      <c r="BU6" s="352"/>
+      <c r="BS6" s="356"/>
+      <c r="BT6" s="356"/>
+      <c r="BU6" s="374"/>
       <c r="BV6"/>
-      <c r="BW6" s="355"/>
-      <c r="BX6" s="342"/>
-      <c r="BY6" s="343"/>
-      <c r="BZ6" s="343"/>
-      <c r="CA6" s="344"/>
-      <c r="CB6" s="349"/>
-      <c r="CC6" s="245"/>
-      <c r="CD6" s="245"/>
+      <c r="BW6" s="377"/>
+      <c r="BX6" s="365"/>
+      <c r="BY6" s="366"/>
+      <c r="BZ6" s="366"/>
+      <c r="CA6" s="367"/>
+      <c r="CB6" s="372"/>
+      <c r="CC6" s="304"/>
+      <c r="CD6" s="304"/>
       <c r="CH6" s="35"/>
       <c r="CI6" s="36"/>
     </row>
     <row r="7" spans="1:87" s="34" customFormat="1">
-      <c r="A7" s="370"/>
-      <c r="B7" s="373"/>
-      <c r="C7" s="321"/>
-      <c r="D7" s="376"/>
-      <c r="E7" s="376"/>
-      <c r="F7" s="410"/>
-      <c r="G7" s="321"/>
-      <c r="H7" s="334"/>
-      <c r="I7" s="334"/>
-      <c r="J7" s="321"/>
-      <c r="K7" s="358"/>
-      <c r="L7" s="358"/>
-      <c r="M7" s="358"/>
-      <c r="N7" s="358"/>
-      <c r="O7" s="358"/>
-      <c r="P7" s="358"/>
-      <c r="Q7" s="358"/>
-      <c r="R7" s="358"/>
-      <c r="S7" s="358"/>
-      <c r="T7" s="358"/>
-      <c r="U7" s="358"/>
-      <c r="V7" s="365"/>
-      <c r="W7" s="366"/>
-      <c r="X7" s="358"/>
-      <c r="Y7" s="321"/>
-      <c r="Z7" s="321"/>
-      <c r="AA7" s="321"/>
-      <c r="AB7" s="321"/>
-      <c r="AC7" s="334"/>
-      <c r="AD7" s="334"/>
-      <c r="AE7" s="334"/>
-      <c r="AF7" s="334"/>
-      <c r="AG7" s="321"/>
-      <c r="AH7" s="334"/>
-      <c r="AI7" s="334"/>
-      <c r="AJ7" s="321"/>
-      <c r="AK7" s="337"/>
-      <c r="AL7" s="321"/>
-      <c r="AM7" s="321"/>
-      <c r="AN7" s="248"/>
-      <c r="AO7" s="321"/>
-      <c r="AP7" s="321"/>
-      <c r="AQ7" s="321"/>
-      <c r="AR7" s="321"/>
-      <c r="AS7" s="321"/>
-      <c r="AT7" s="321"/>
-      <c r="AU7" s="321"/>
-      <c r="AV7" s="321"/>
-      <c r="AW7" s="321"/>
-      <c r="AX7" s="321"/>
+      <c r="A7" s="324"/>
+      <c r="B7" s="327"/>
+      <c r="C7" s="330"/>
+      <c r="D7" s="333"/>
+      <c r="E7" s="333"/>
+      <c r="F7" s="413"/>
+      <c r="G7" s="330"/>
+      <c r="H7" s="336"/>
+      <c r="I7" s="336"/>
+      <c r="J7" s="330"/>
+      <c r="K7" s="344"/>
+      <c r="L7" s="344"/>
+      <c r="M7" s="344"/>
+      <c r="N7" s="344"/>
+      <c r="O7" s="344"/>
+      <c r="P7" s="344"/>
+      <c r="Q7" s="344"/>
+      <c r="R7" s="344"/>
+      <c r="S7" s="344"/>
+      <c r="T7" s="344"/>
+      <c r="U7" s="344"/>
+      <c r="V7" s="348"/>
+      <c r="W7" s="349"/>
+      <c r="X7" s="344"/>
+      <c r="Y7" s="330"/>
+      <c r="Z7" s="330"/>
+      <c r="AA7" s="330"/>
+      <c r="AB7" s="330"/>
+      <c r="AC7" s="336"/>
+      <c r="AD7" s="336"/>
+      <c r="AE7" s="336"/>
+      <c r="AF7" s="336"/>
+      <c r="AG7" s="330"/>
+      <c r="AH7" s="336"/>
+      <c r="AI7" s="336"/>
+      <c r="AJ7" s="330"/>
+      <c r="AK7" s="380"/>
+      <c r="AL7" s="330"/>
+      <c r="AM7" s="330"/>
+      <c r="AN7" s="262"/>
+      <c r="AO7" s="330"/>
+      <c r="AP7" s="330"/>
+      <c r="AQ7" s="330"/>
+      <c r="AR7" s="330"/>
+      <c r="AS7" s="330"/>
+      <c r="AT7" s="330"/>
+      <c r="AU7" s="330"/>
+      <c r="AV7" s="330"/>
+      <c r="AW7" s="330"/>
+      <c r="AX7" s="330"/>
       <c r="AY7" s="16" t="s">
         <v>68</v>
       </c>
@@ -17968,123 +17977,123 @@
       <c r="BA7" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="BB7" s="328" t="s">
+      <c r="BB7" s="355" t="s">
         <v>71</v>
       </c>
-      <c r="BC7" s="329" t="s">
+      <c r="BC7" s="358" t="s">
         <v>72</v>
       </c>
-      <c r="BD7" s="329" t="s">
+      <c r="BD7" s="358" t="s">
         <v>73</v>
       </c>
-      <c r="BE7" s="329" t="s">
+      <c r="BE7" s="358" t="s">
         <v>146</v>
       </c>
-      <c r="BF7" s="329" t="s">
+      <c r="BF7" s="358" t="s">
         <v>75</v>
       </c>
-      <c r="BG7" s="329" t="s">
+      <c r="BG7" s="358" t="s">
         <v>76</v>
       </c>
-      <c r="BH7" s="329" t="s">
+      <c r="BH7" s="358" t="s">
         <v>77</v>
       </c>
-      <c r="BI7" s="329" t="s">
+      <c r="BI7" s="358" t="s">
         <v>80</v>
       </c>
-      <c r="BJ7" s="331" t="s">
+      <c r="BJ7" s="382" t="s">
         <v>81</v>
       </c>
-      <c r="BK7" s="329" t="s">
+      <c r="BK7" s="358" t="s">
         <v>82</v>
       </c>
-      <c r="BL7" s="328" t="s">
+      <c r="BL7" s="355" t="s">
         <v>83</v>
       </c>
-      <c r="BM7" s="329" t="s">
+      <c r="BM7" s="358" t="s">
         <v>84</v>
       </c>
-      <c r="BN7" s="328" t="s">
+      <c r="BN7" s="355" t="s">
         <v>85</v>
       </c>
-      <c r="BO7" s="328" t="s">
+      <c r="BO7" s="355" t="s">
         <v>147</v>
       </c>
-      <c r="BP7" s="328" t="s">
+      <c r="BP7" s="355" t="s">
         <v>86</v>
       </c>
-      <c r="BQ7" s="326"/>
-      <c r="BR7" s="326"/>
-      <c r="BS7" s="326"/>
-      <c r="BT7" s="326"/>
-      <c r="BU7" s="352"/>
+      <c r="BQ7" s="356"/>
+      <c r="BR7" s="356"/>
+      <c r="BS7" s="356"/>
+      <c r="BT7" s="356"/>
+      <c r="BU7" s="374"/>
       <c r="BV7"/>
-      <c r="BW7" s="356"/>
-      <c r="BX7" s="345"/>
-      <c r="BY7" s="346"/>
-      <c r="BZ7" s="346"/>
-      <c r="CA7" s="347"/>
-      <c r="CB7" s="350"/>
-      <c r="CC7" s="246"/>
-      <c r="CD7" s="246"/>
+      <c r="BW7" s="378"/>
+      <c r="BX7" s="368"/>
+      <c r="BY7" s="369"/>
+      <c r="BZ7" s="369"/>
+      <c r="CA7" s="370"/>
+      <c r="CB7" s="373"/>
+      <c r="CC7" s="305"/>
+      <c r="CD7" s="305"/>
       <c r="CH7" s="35"/>
       <c r="CI7" s="36"/>
     </row>
     <row r="8" spans="1:87" s="34" customFormat="1" ht="24">
-      <c r="A8" s="371"/>
-      <c r="B8" s="374"/>
-      <c r="C8" s="322"/>
-      <c r="D8" s="377"/>
-      <c r="E8" s="377"/>
-      <c r="F8" s="411"/>
-      <c r="G8" s="322"/>
-      <c r="H8" s="335"/>
-      <c r="I8" s="335"/>
-      <c r="J8" s="322"/>
-      <c r="K8" s="359"/>
-      <c r="L8" s="359"/>
-      <c r="M8" s="359"/>
-      <c r="N8" s="359"/>
-      <c r="O8" s="359"/>
-      <c r="P8" s="359"/>
-      <c r="Q8" s="359"/>
-      <c r="R8" s="359"/>
-      <c r="S8" s="359"/>
-      <c r="T8" s="359"/>
-      <c r="U8" s="359"/>
+      <c r="A8" s="325"/>
+      <c r="B8" s="328"/>
+      <c r="C8" s="331"/>
+      <c r="D8" s="334"/>
+      <c r="E8" s="334"/>
+      <c r="F8" s="414"/>
+      <c r="G8" s="331"/>
+      <c r="H8" s="337"/>
+      <c r="I8" s="337"/>
+      <c r="J8" s="331"/>
+      <c r="K8" s="345"/>
+      <c r="L8" s="345"/>
+      <c r="M8" s="345"/>
+      <c r="N8" s="345"/>
+      <c r="O8" s="345"/>
+      <c r="P8" s="345"/>
+      <c r="Q8" s="345"/>
+      <c r="R8" s="345"/>
+      <c r="S8" s="345"/>
+      <c r="T8" s="345"/>
+      <c r="U8" s="345"/>
       <c r="V8" s="38" t="s">
         <v>87</v>
       </c>
       <c r="W8" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="X8" s="359"/>
-      <c r="Y8" s="322"/>
-      <c r="Z8" s="322"/>
-      <c r="AA8" s="322"/>
-      <c r="AB8" s="322"/>
-      <c r="AC8" s="335"/>
-      <c r="AD8" s="335"/>
-      <c r="AE8" s="335"/>
-      <c r="AF8" s="335"/>
-      <c r="AG8" s="322"/>
-      <c r="AH8" s="335"/>
-      <c r="AI8" s="335"/>
-      <c r="AJ8" s="322"/>
-      <c r="AK8" s="338"/>
-      <c r="AL8" s="322"/>
-      <c r="AM8" s="322"/>
-      <c r="AN8" s="249"/>
-      <c r="AO8" s="322"/>
-      <c r="AP8" s="322"/>
-      <c r="AQ8" s="322"/>
-      <c r="AR8" s="322"/>
-      <c r="AS8" s="322"/>
-      <c r="AT8" s="322"/>
-      <c r="AU8" s="322"/>
-      <c r="AV8" s="322"/>
-      <c r="AW8" s="322"/>
-      <c r="AX8" s="322"/>
+      <c r="X8" s="345"/>
+      <c r="Y8" s="331"/>
+      <c r="Z8" s="331"/>
+      <c r="AA8" s="331"/>
+      <c r="AB8" s="331"/>
+      <c r="AC8" s="337"/>
+      <c r="AD8" s="337"/>
+      <c r="AE8" s="337"/>
+      <c r="AF8" s="337"/>
+      <c r="AG8" s="331"/>
+      <c r="AH8" s="337"/>
+      <c r="AI8" s="337"/>
+      <c r="AJ8" s="331"/>
+      <c r="AK8" s="381"/>
+      <c r="AL8" s="331"/>
+      <c r="AM8" s="331"/>
+      <c r="AN8" s="263"/>
+      <c r="AO8" s="331"/>
+      <c r="AP8" s="331"/>
+      <c r="AQ8" s="331"/>
+      <c r="AR8" s="331"/>
+      <c r="AS8" s="331"/>
+      <c r="AT8" s="331"/>
+      <c r="AU8" s="331"/>
+      <c r="AV8" s="331"/>
+      <c r="AW8" s="331"/>
+      <c r="AX8" s="331"/>
       <c r="AY8" s="17" t="s">
         <v>89</v>
       </c>
@@ -18094,28 +18103,28 @@
       <c r="BA8" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="BB8" s="327"/>
-      <c r="BC8" s="330"/>
-      <c r="BD8" s="330"/>
-      <c r="BE8" s="330"/>
-      <c r="BF8" s="330"/>
-      <c r="BG8" s="330"/>
-      <c r="BH8" s="330"/>
-      <c r="BI8" s="330"/>
-      <c r="BJ8" s="332"/>
-      <c r="BK8" s="330"/>
-      <c r="BL8" s="327"/>
-      <c r="BM8" s="330"/>
-      <c r="BN8" s="327"/>
-      <c r="BO8" s="327"/>
-      <c r="BP8" s="327"/>
-      <c r="BQ8" s="327"/>
-      <c r="BR8" s="327"/>
-      <c r="BS8" s="327"/>
-      <c r="BT8" s="327"/>
-      <c r="BU8" s="353"/>
+      <c r="BB8" s="357"/>
+      <c r="BC8" s="359"/>
+      <c r="BD8" s="359"/>
+      <c r="BE8" s="359"/>
+      <c r="BF8" s="359"/>
+      <c r="BG8" s="359"/>
+      <c r="BH8" s="359"/>
+      <c r="BI8" s="359"/>
+      <c r="BJ8" s="383"/>
+      <c r="BK8" s="359"/>
+      <c r="BL8" s="357"/>
+      <c r="BM8" s="359"/>
+      <c r="BN8" s="357"/>
+      <c r="BO8" s="357"/>
+      <c r="BP8" s="357"/>
+      <c r="BQ8" s="357"/>
+      <c r="BR8" s="357"/>
+      <c r="BS8" s="357"/>
+      <c r="BT8" s="357"/>
+      <c r="BU8" s="375"/>
       <c r="BV8"/>
-      <c r="BW8" s="356"/>
+      <c r="BW8" s="378"/>
       <c r="BX8" s="8" t="s">
         <v>92</v>
       </c>
@@ -18128,9 +18137,9 @@
       <c r="CA8" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="CB8" s="350"/>
-      <c r="CC8" s="246"/>
-      <c r="CD8" s="246"/>
+      <c r="CB8" s="373"/>
+      <c r="CC8" s="305"/>
+      <c r="CD8" s="305"/>
       <c r="CF8" s="39"/>
       <c r="CH8" s="35"/>
       <c r="CI8" s="36"/>
@@ -20307,24 +20316,54 @@
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="82">
-    <mergeCell ref="BK6:BP6"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="AY6:BJ6"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="AY5:BP5"/>
+    <mergeCell ref="BQ5:BR5"/>
+    <mergeCell ref="BS5:BS8"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="BQ6:BQ8"/>
     <mergeCell ref="BX5:CA7"/>
     <mergeCell ref="CB5:CB8"/>
     <mergeCell ref="CC5:CC8"/>
@@ -20341,71 +20380,41 @@
     <mergeCell ref="BF7:BF8"/>
     <mergeCell ref="BG7:BG8"/>
     <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BQ6:BQ8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="AY5:BP5"/>
-    <mergeCell ref="BQ5:BR5"/>
-    <mergeCell ref="BS5:BS8"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="AY6:BJ6"/>
+    <mergeCell ref="BK6:BP6"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="BJ7:BJ8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 C9:BU9 B20:B1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B9 B12:B16 D10:F10 J10:BI10 BK10:BU10 C9:BU9 B20:B1048576 BW9:CD10">
-    <cfRule type="duplicateValues" dxfId="6" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:B16 B1:B9 C9:BU9 B20:B1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ10">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.21" bottom="0.17" header="0.196850393700787" footer="0.196850393700787"/>

--- a/thaco/API/1 MID- VPTQ THACO-11FEBv2.xlsx
+++ b/thaco/API/1 MID- VPTQ THACO-11FEBv2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/API/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C28240B-056C-BE41-AADB-0E19068EF2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49714E4-F4C5-EF40-B6CF-4354BB9F3A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="761" activeTab="2" xr2:uid="{D2D6ECD8-DC99-4D28-8DAC-0623419D46D2}"/>
   </bookViews>
